--- a/research/traditional_assets/database/data/australia/australia_transportation_railroads.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_transportation_railroads.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0671704332164582</v>
+        <v>0.06700042191680881</v>
       </c>
       <c r="C2">
-        <v>6123.189629207231</v>
+        <v>6070.325203696455</v>
       </c>
       <c r="D2">
-        <v>6090.489629207231</v>
+        <v>6108.781203696455</v>
       </c>
       <c r="E2">
-        <v>-3548.8</v>
+        <v>-3477.644</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>71.15600000000001</v>
       </c>
       <c r="G2">
         <v>32.7</v>
@@ -1457,28 +1457,28 @@
         <v>843.55</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.5791468</v>
       </c>
       <c r="N2">
-        <v>843.55</v>
+        <v>839.9708532</v>
       </c>
       <c r="O2">
-        <v>253.065</v>
+        <v>251.99125596</v>
       </c>
       <c r="P2">
-        <v>590.485</v>
+        <v>587.97959724</v>
       </c>
       <c r="Q2">
-        <v>1062.185</v>
+        <v>1059.67959724</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0671704332164582</v>
+        <v>0.06732153728970589</v>
       </c>
       <c r="T2">
-        <v>0.4935434922969562</v>
+        <v>0.4970331937576417</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>235.6846609365114</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06700042191680881</v>
+        <v>0.06683041061715946</v>
       </c>
       <c r="C3">
-        <v>6070.325203696455</v>
+        <v>6017.570979366297</v>
       </c>
       <c r="D3">
-        <v>6108.781203696455</v>
+        <v>6127.182979366297</v>
       </c>
       <c r="E3">
-        <v>-3477.644</v>
+        <v>-3406.488</v>
       </c>
       <c r="F3">
-        <v>71.15600000000001</v>
+        <v>142.312</v>
       </c>
       <c r="G3">
         <v>32.7</v>
@@ -1539,28 +1539,28 @@
         <v>843.55</v>
       </c>
       <c r="M3">
-        <v>3.5791468</v>
+        <v>7.1582936</v>
       </c>
       <c r="N3">
-        <v>839.9708532</v>
+        <v>836.3917064</v>
       </c>
       <c r="O3">
-        <v>251.99125596</v>
+        <v>250.91751192</v>
       </c>
       <c r="P3">
-        <v>587.97959724</v>
+        <v>585.4741944800001</v>
       </c>
       <c r="Q3">
-        <v>1059.67959724</v>
+        <v>1057.17419448</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06732153728970589</v>
+        <v>0.06747572511955047</v>
       </c>
       <c r="T3">
-        <v>0.4970331937576417</v>
+        <v>0.5005941136154841</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>235.6846609365114</v>
+        <v>117.8423304682557</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06683041061715946</v>
+        <v>0.06666039931751007</v>
       </c>
       <c r="C4">
-        <v>6017.570979366297</v>
+        <v>5964.927955118766</v>
       </c>
       <c r="D4">
-        <v>6127.182979366297</v>
+        <v>6145.695955118766</v>
       </c>
       <c r="E4">
-        <v>-3406.488</v>
+        <v>-3335.332</v>
       </c>
       <c r="F4">
-        <v>142.312</v>
+        <v>213.468</v>
       </c>
       <c r="G4">
         <v>32.7</v>
@@ -1621,28 +1621,28 @@
         <v>843.55</v>
       </c>
       <c r="M4">
-        <v>7.1582936</v>
+        <v>10.7374404</v>
       </c>
       <c r="N4">
-        <v>836.3917064</v>
+        <v>832.8125596</v>
       </c>
       <c r="O4">
-        <v>250.91751192</v>
+        <v>249.84376788</v>
       </c>
       <c r="P4">
-        <v>585.4741944800001</v>
+        <v>582.96879172</v>
       </c>
       <c r="Q4">
-        <v>1057.17419448</v>
+        <v>1054.66879172</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06747572511955047</v>
+        <v>0.06763309207990729</v>
       </c>
       <c r="T4">
-        <v>0.5005941136154841</v>
+        <v>0.5042284545013233</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>117.8423304682557</v>
+        <v>78.56155364550382</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06666039931751007</v>
+        <v>0.06649038801786071</v>
       </c>
       <c r="C5">
-        <v>5964.927955118766</v>
+        <v>5912.397141964975</v>
       </c>
       <c r="D5">
-        <v>6145.695955118766</v>
+        <v>6164.321141964975</v>
       </c>
       <c r="E5">
-        <v>-3335.332</v>
+        <v>-3264.176</v>
       </c>
       <c r="F5">
-        <v>213.468</v>
+        <v>284.624</v>
       </c>
       <c r="G5">
         <v>32.7</v>
@@ -1703,28 +1703,28 @@
         <v>843.55</v>
       </c>
       <c r="M5">
-        <v>10.7374404</v>
+        <v>14.3165872</v>
       </c>
       <c r="N5">
-        <v>832.8125596</v>
+        <v>829.2334128</v>
       </c>
       <c r="O5">
-        <v>249.84376788</v>
+        <v>248.77002384</v>
       </c>
       <c r="P5">
-        <v>582.96879172</v>
+        <v>580.46338896</v>
       </c>
       <c r="Q5">
-        <v>1054.66879172</v>
+        <v>1052.16338896</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06763309207990729</v>
+        <v>0.0677937375186049</v>
       </c>
       <c r="T5">
-        <v>0.5042284545013233</v>
+        <v>0.507938510822284</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>78.56155364550382</v>
+        <v>58.92116523412786</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06649038801786071</v>
+        <v>0.06632037671821132</v>
       </c>
       <c r="C6">
-        <v>5912.397141964975</v>
+        <v>5859.979563209213</v>
       </c>
       <c r="D6">
-        <v>6164.321141964975</v>
+        <v>6183.059563209213</v>
       </c>
       <c r="E6">
-        <v>-3264.176</v>
+        <v>-3193.02</v>
       </c>
       <c r="F6">
-        <v>284.624</v>
+        <v>355.78</v>
       </c>
       <c r="G6">
         <v>32.7</v>
@@ -1785,28 +1785,28 @@
         <v>843.55</v>
       </c>
       <c r="M6">
-        <v>14.3165872</v>
+        <v>17.895734</v>
       </c>
       <c r="N6">
-        <v>829.2334128</v>
+        <v>825.654266</v>
       </c>
       <c r="O6">
-        <v>248.77002384</v>
+        <v>247.6962798</v>
       </c>
       <c r="P6">
-        <v>580.46338896</v>
+        <v>577.9579862000001</v>
       </c>
       <c r="Q6">
-        <v>1052.16338896</v>
+        <v>1049.6579862</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0677937375186049</v>
+        <v>0.06795776496653824</v>
       </c>
       <c r="T6">
-        <v>0.507938510822284</v>
+        <v>0.5117266735921071</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>58.92116523412786</v>
+        <v>47.13693218730229</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06632037671821132</v>
+        <v>0.06615036541856195</v>
       </c>
       <c r="C7">
-        <v>5859.979563209213</v>
+        <v>5807.676254636339</v>
       </c>
       <c r="D7">
-        <v>6183.059563209213</v>
+        <v>6201.912254636339</v>
       </c>
       <c r="E7">
-        <v>-3193.02</v>
+        <v>-3121.864</v>
       </c>
       <c r="F7">
-        <v>355.78</v>
+        <v>426.936</v>
       </c>
       <c r="G7">
         <v>32.7</v>
@@ -1867,28 +1867,28 @@
         <v>843.55</v>
       </c>
       <c r="M7">
-        <v>17.895734</v>
+        <v>21.4748808</v>
       </c>
       <c r="N7">
-        <v>825.654266</v>
+        <v>822.0751191999999</v>
       </c>
       <c r="O7">
-        <v>247.6962798</v>
+        <v>246.6225357599999</v>
       </c>
       <c r="P7">
-        <v>577.9579862000001</v>
+        <v>575.4525834399999</v>
       </c>
       <c r="Q7">
-        <v>1049.6579862</v>
+        <v>1047.15258344</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06795776496653824</v>
+        <v>0.06812528236017229</v>
       </c>
       <c r="T7">
-        <v>0.5117266735921071</v>
+        <v>0.5155954355697988</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>47.13693218730229</v>
+        <v>39.2807768227519</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06615036541856195</v>
+        <v>0.06598035411891258</v>
       </c>
       <c r="C8">
-        <v>5807.676254636339</v>
+        <v>5755.488264702647</v>
       </c>
       <c r="D8">
-        <v>6201.912254636339</v>
+        <v>6220.880264702647</v>
       </c>
       <c r="E8">
-        <v>-3121.864</v>
+        <v>-3050.708</v>
       </c>
       <c r="F8">
-        <v>426.936</v>
+        <v>498.092</v>
       </c>
       <c r="G8">
         <v>32.7</v>
@@ -1949,28 +1949,28 @@
         <v>843.55</v>
       </c>
       <c r="M8">
-        <v>21.4748808</v>
+        <v>25.0540276</v>
       </c>
       <c r="N8">
-        <v>822.0751191999999</v>
+        <v>818.4959723999999</v>
       </c>
       <c r="O8">
-        <v>246.6225357599999</v>
+        <v>245.54879172</v>
       </c>
       <c r="P8">
-        <v>575.4525834399999</v>
+        <v>572.94718068</v>
       </c>
       <c r="Q8">
-        <v>1047.15258344</v>
+        <v>1044.64718068</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.06812528236017229</v>
+        <v>0.06829640227840061</v>
       </c>
       <c r="T8">
-        <v>0.5155954355697988</v>
+        <v>0.5195473967298065</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>39.28077682275191</v>
+        <v>33.66923727664449</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06598035411891257</v>
+        <v>0.06581034281926321</v>
       </c>
       <c r="C9">
-        <v>5755.488264702648</v>
+        <v>5703.41665473023</v>
       </c>
       <c r="D9">
-        <v>6220.880264702648</v>
+        <v>6239.96465473023</v>
       </c>
       <c r="E9">
-        <v>-3050.708</v>
+        <v>-2979.552</v>
       </c>
       <c r="F9">
-        <v>498.0920000000001</v>
+        <v>569.248</v>
       </c>
       <c r="G9">
         <v>32.7</v>
@@ -2031,28 +2031,28 @@
         <v>843.55</v>
       </c>
       <c r="M9">
-        <v>25.0540276</v>
+        <v>28.6331744</v>
       </c>
       <c r="N9">
-        <v>818.4959723999999</v>
+        <v>814.9168255999999</v>
       </c>
       <c r="O9">
-        <v>245.54879172</v>
+        <v>244.47504768</v>
       </c>
       <c r="P9">
-        <v>572.94718068</v>
+        <v>570.4417779199999</v>
       </c>
       <c r="Q9">
-        <v>1044.64718068</v>
+        <v>1042.14177792</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.06829640227840061</v>
+        <v>0.06847124219485132</v>
       </c>
       <c r="T9">
-        <v>0.5195473967298065</v>
+        <v>0.5235852700889448</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>33.66923727664449</v>
+        <v>29.46058261706393</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06581034281926321</v>
+        <v>0.06564033151961382</v>
       </c>
       <c r="C10">
-        <v>5703.41665473023</v>
+        <v>5651.462499104937</v>
       </c>
       <c r="D10">
-        <v>6239.96465473023</v>
+        <v>6259.166499104937</v>
       </c>
       <c r="E10">
-        <v>-2979.552</v>
+        <v>-2908.396</v>
       </c>
       <c r="F10">
-        <v>569.248</v>
+        <v>640.404</v>
       </c>
       <c r="G10">
         <v>32.7</v>
@@ -2113,28 +2113,28 @@
         <v>843.55</v>
       </c>
       <c r="M10">
-        <v>28.6331744</v>
+        <v>32.2123212</v>
       </c>
       <c r="N10">
-        <v>814.9168255999999</v>
+        <v>811.3376787999999</v>
       </c>
       <c r="O10">
-        <v>244.47504768</v>
+        <v>243.40130364</v>
       </c>
       <c r="P10">
-        <v>570.4417779199999</v>
+        <v>567.9363751599999</v>
       </c>
       <c r="Q10">
-        <v>1042.14177792</v>
+        <v>1039.63637516</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.06847124219485132</v>
+        <v>0.06864992474682838</v>
       </c>
       <c r="T10">
-        <v>0.5235852700889448</v>
+        <v>0.5277118879175147</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>29.46058261706393</v>
+        <v>26.18718454850127</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06564033151961382</v>
+        <v>0.06547032021996445</v>
       </c>
       <c r="C11">
-        <v>5651.462499104937</v>
+        <v>5599.626885477992</v>
       </c>
       <c r="D11">
-        <v>6259.166499104937</v>
+        <v>6278.486885477992</v>
       </c>
       <c r="E11">
-        <v>-2908.396</v>
+        <v>-2837.24</v>
       </c>
       <c r="F11">
-        <v>640.404</v>
+        <v>711.5599999999999</v>
       </c>
       <c r="G11">
         <v>32.7</v>
@@ -2195,28 +2195,28 @@
         <v>843.55</v>
       </c>
       <c r="M11">
-        <v>32.2123212</v>
+        <v>35.79146799999999</v>
       </c>
       <c r="N11">
-        <v>811.3376787999999</v>
+        <v>807.7585319999999</v>
       </c>
       <c r="O11">
-        <v>243.40130364</v>
+        <v>242.3275596</v>
       </c>
       <c r="P11">
-        <v>567.9363751599999</v>
+        <v>565.4309724</v>
       </c>
       <c r="Q11">
-        <v>1039.63637516</v>
+        <v>1037.1309724</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.06864992474682838</v>
+        <v>0.06883257802218272</v>
       </c>
       <c r="T11">
-        <v>0.5277118879175147</v>
+        <v>0.5319302083644971</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>26.18718454850127</v>
+        <v>23.56846609365115</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06547032021996445</v>
+        <v>0.06530030892031508</v>
       </c>
       <c r="C12">
-        <v>5599.626885477991</v>
+        <v>5547.910914971358</v>
       </c>
       <c r="D12">
-        <v>6278.486885477992</v>
+        <v>6297.926914971358</v>
       </c>
       <c r="E12">
-        <v>-2837.24</v>
+        <v>-2766.084</v>
       </c>
       <c r="F12">
-        <v>711.5600000000001</v>
+        <v>782.716</v>
       </c>
       <c r="G12">
         <v>32.7</v>
@@ -2277,28 +2277,28 @@
         <v>843.55</v>
       </c>
       <c r="M12">
-        <v>35.791468</v>
+        <v>39.3706148</v>
       </c>
       <c r="N12">
-        <v>807.7585319999999</v>
+        <v>804.1793852</v>
       </c>
       <c r="O12">
-        <v>242.3275596</v>
+        <v>241.25381556</v>
       </c>
       <c r="P12">
-        <v>565.4309724</v>
+        <v>562.92556964</v>
       </c>
       <c r="Q12">
-        <v>1037.1309724</v>
+        <v>1034.62556964</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.06883257802218272</v>
+        <v>0.06901933586552256</v>
       </c>
       <c r="T12">
-        <v>0.5319302083644971</v>
+        <v>0.5362433225293894</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>23.56846609365114</v>
+        <v>21.42587826695559</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06530030892031508</v>
+        <v>0.0651302976206657</v>
       </c>
       <c r="C13">
-        <v>5547.910914971358</v>
+        <v>5496.315702386945</v>
       </c>
       <c r="D13">
-        <v>6297.926914971358</v>
+        <v>6317.487702386946</v>
       </c>
       <c r="E13">
-        <v>-2766.084</v>
+        <v>-2694.928</v>
       </c>
       <c r="F13">
-        <v>782.716</v>
+        <v>853.872</v>
       </c>
       <c r="G13">
         <v>32.7</v>
@@ -2359,28 +2359,28 @@
         <v>843.55</v>
       </c>
       <c r="M13">
-        <v>39.3706148</v>
+        <v>42.9497616</v>
       </c>
       <c r="N13">
-        <v>804.1793852</v>
+        <v>800.6002384</v>
       </c>
       <c r="O13">
-        <v>241.25381556</v>
+        <v>240.18007152</v>
       </c>
       <c r="P13">
-        <v>562.92556964</v>
+        <v>560.42016688</v>
       </c>
       <c r="Q13">
-        <v>1034.62556964</v>
+        <v>1032.12016688</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.06901933586552256</v>
+        <v>0.06921033820530194</v>
       </c>
       <c r="T13">
-        <v>0.5362433225293894</v>
+        <v>0.540654462016211</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>21.42587826695559</v>
+        <v>19.64038841137596</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0651302976206657</v>
+        <v>0.06496028632101633</v>
       </c>
       <c r="C14">
-        <v>5496.315702386945</v>
+        <v>5444.842376419701</v>
       </c>
       <c r="D14">
-        <v>6317.487702386946</v>
+        <v>6337.170376419702</v>
       </c>
       <c r="E14">
-        <v>-2694.928</v>
+        <v>-2623.772</v>
       </c>
       <c r="F14">
-        <v>853.872</v>
+        <v>925.0280000000001</v>
       </c>
       <c r="G14">
         <v>32.7</v>
@@ -2441,28 +2441,28 @@
         <v>843.55</v>
       </c>
       <c r="M14">
-        <v>42.9497616</v>
+        <v>46.52890840000001</v>
       </c>
       <c r="N14">
-        <v>800.6002384</v>
+        <v>797.0210916</v>
       </c>
       <c r="O14">
-        <v>240.18007152</v>
+        <v>239.10632748</v>
       </c>
       <c r="P14">
-        <v>560.42016688</v>
+        <v>557.91476412</v>
       </c>
       <c r="Q14">
-        <v>1032.12016688</v>
+        <v>1029.61476412</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.06921033820530194</v>
+        <v>0.06940573140346705</v>
       </c>
       <c r="T14">
-        <v>0.540654462016211</v>
+        <v>0.5451670070084769</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.64038841137596</v>
+        <v>18.12958930280857</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06496028632101633</v>
+        <v>0.06479027502136696</v>
       </c>
       <c r="C15">
-        <v>5444.842376419701</v>
+        <v>5393.49207987472</v>
       </c>
       <c r="D15">
-        <v>6337.170376419702</v>
+        <v>6356.97607987472</v>
       </c>
       <c r="E15">
-        <v>-2623.772</v>
+        <v>-2552.616</v>
       </c>
       <c r="F15">
-        <v>925.0280000000001</v>
+        <v>996.1840000000002</v>
       </c>
       <c r="G15">
         <v>32.7</v>
@@ -2523,28 +2523,28 @@
         <v>843.55</v>
       </c>
       <c r="M15">
-        <v>46.52890840000001</v>
+        <v>50.10805520000001</v>
       </c>
       <c r="N15">
-        <v>797.0210916</v>
+        <v>793.4419448</v>
       </c>
       <c r="O15">
-        <v>239.10632748</v>
+        <v>238.03258344</v>
       </c>
       <c r="P15">
-        <v>557.91476412</v>
+        <v>555.40936136</v>
       </c>
       <c r="Q15">
-        <v>1029.61476412</v>
+        <v>1027.10936136</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.06940573140346705</v>
+        <v>0.06960566862949646</v>
       </c>
       <c r="T15">
-        <v>0.5451670070084769</v>
+        <v>0.5497844949075394</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>18.12958930280857</v>
+        <v>16.83461863832224</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06479027502136696</v>
+        <v>0.06462026372171757</v>
       </c>
       <c r="C16">
-        <v>5393.49207987472</v>
+        <v>5342.265969888425</v>
       </c>
       <c r="D16">
-        <v>6356.97607987472</v>
+        <v>6376.905969888426</v>
       </c>
       <c r="E16">
-        <v>-2552.616</v>
+        <v>-2481.46</v>
       </c>
       <c r="F16">
-        <v>996.1840000000002</v>
+        <v>1067.34</v>
       </c>
       <c r="G16">
         <v>32.7</v>
@@ -2605,28 +2605,28 @@
         <v>843.55</v>
       </c>
       <c r="M16">
-        <v>50.10805520000001</v>
+        <v>53.68720200000001</v>
       </c>
       <c r="N16">
-        <v>793.4419448</v>
+        <v>789.862798</v>
       </c>
       <c r="O16">
-        <v>238.03258344</v>
+        <v>236.9588394</v>
       </c>
       <c r="P16">
-        <v>555.40936136</v>
+        <v>552.9039586</v>
       </c>
       <c r="Q16">
-        <v>1027.10936136</v>
+        <v>1024.6039586</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.06960566862949646</v>
+        <v>0.06981031026084421</v>
       </c>
       <c r="T16">
-        <v>0.5497844949075394</v>
+        <v>0.5545106295806977</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.83461863832224</v>
+        <v>15.71231072910076</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06462026372171757</v>
+        <v>0.0644502524220682</v>
       </c>
       <c r="C17">
-        <v>5342.265969888425</v>
+        <v>5291.165218153927</v>
       </c>
       <c r="D17">
-        <v>6376.905969888426</v>
+        <v>6396.961218153927</v>
       </c>
       <c r="E17">
-        <v>-2481.46</v>
+        <v>-2410.304</v>
       </c>
       <c r="F17">
-        <v>1067.34</v>
+        <v>1138.496</v>
       </c>
       <c r="G17">
         <v>32.7</v>
@@ -2687,28 +2687,28 @@
         <v>843.55</v>
       </c>
       <c r="M17">
-        <v>53.68720199999999</v>
+        <v>57.2663488</v>
       </c>
       <c r="N17">
-        <v>789.862798</v>
+        <v>786.2836511999999</v>
       </c>
       <c r="O17">
-        <v>236.9588394</v>
+        <v>235.88509536</v>
       </c>
       <c r="P17">
-        <v>552.9039586</v>
+        <v>550.39855584</v>
       </c>
       <c r="Q17">
-        <v>1024.6039586</v>
+        <v>1022.09855584</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.06981031026084421</v>
+        <v>0.07001982431198596</v>
       </c>
       <c r="T17">
-        <v>0.5545106295806977</v>
+        <v>0.5593492912698836</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.71231072910077</v>
+        <v>14.73029130853196</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0644502524220682</v>
+        <v>0.06428024112241884</v>
       </c>
       <c r="C18">
-        <v>5291.165218153927</v>
+        <v>5240.191011150647</v>
       </c>
       <c r="D18">
-        <v>6396.961218153927</v>
+        <v>6417.143011150647</v>
       </c>
       <c r="E18">
-        <v>-2410.304</v>
+        <v>-2339.148</v>
       </c>
       <c r="F18">
-        <v>1138.496</v>
+        <v>1209.652</v>
       </c>
       <c r="G18">
         <v>32.7</v>
@@ -2769,28 +2769,28 @@
         <v>843.55</v>
       </c>
       <c r="M18">
-        <v>57.2663488</v>
+        <v>60.8454956</v>
       </c>
       <c r="N18">
-        <v>786.2836511999999</v>
+        <v>782.7045043999999</v>
       </c>
       <c r="O18">
-        <v>235.88509536</v>
+        <v>234.81135132</v>
       </c>
       <c r="P18">
-        <v>550.39855584</v>
+        <v>547.8931530799999</v>
       </c>
       <c r="Q18">
-        <v>1022.09855584</v>
+        <v>1019.59315308</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07001982431198596</v>
+        <v>0.07023438689448053</v>
       </c>
       <c r="T18">
-        <v>0.5593492912698836</v>
+        <v>0.5643045472166403</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.73029130853196</v>
+        <v>13.86380358450067</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06428024112241884</v>
+        <v>0.06411022982276945</v>
       </c>
       <c r="C19">
-        <v>5240.191011150647</v>
+        <v>5189.344550378315</v>
       </c>
       <c r="D19">
-        <v>6417.143011150647</v>
+        <v>6437.452550378315</v>
       </c>
       <c r="E19">
-        <v>-2339.148</v>
+        <v>-2267.992</v>
       </c>
       <c r="F19">
-        <v>1209.652</v>
+        <v>1280.808</v>
       </c>
       <c r="G19">
         <v>32.7</v>
@@ -2851,28 +2851,28 @@
         <v>843.55</v>
       </c>
       <c r="M19">
-        <v>60.8454956</v>
+        <v>64.42464240000001</v>
       </c>
       <c r="N19">
-        <v>782.7045043999999</v>
+        <v>779.1253575999999</v>
       </c>
       <c r="O19">
-        <v>234.81135132</v>
+        <v>233.73760728</v>
       </c>
       <c r="P19">
-        <v>547.8931530799999</v>
+        <v>545.3877503199999</v>
       </c>
       <c r="Q19">
-        <v>1019.59315308</v>
+        <v>1017.08775032</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07023438689448053</v>
+        <v>0.07045418271069445</v>
       </c>
       <c r="T19">
-        <v>0.5643045472166403</v>
+        <v>0.5693806630645372</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>13.86380358450067</v>
+        <v>13.09359227425063</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06411022982276945</v>
+        <v>0.06413971852312009</v>
       </c>
       <c r="C20">
-        <v>5189.344550378315</v>
+        <v>5114.65662193623</v>
       </c>
       <c r="D20">
-        <v>6437.452550378315</v>
+        <v>6433.92062193623</v>
       </c>
       <c r="E20">
-        <v>-2267.992</v>
+        <v>-2196.836</v>
       </c>
       <c r="F20">
-        <v>1280.808</v>
+        <v>1351.964</v>
       </c>
       <c r="G20">
         <v>32.7</v>
@@ -2933,45 +2933,45 @@
         <v>843.55</v>
       </c>
       <c r="M20">
-        <v>64.4246424</v>
+        <v>70.03173520000001</v>
       </c>
       <c r="N20">
-        <v>779.1253575999999</v>
+        <v>773.5182648</v>
       </c>
       <c r="O20">
-        <v>233.73760728</v>
+        <v>232.05547944</v>
       </c>
       <c r="P20">
-        <v>545.3877503199999</v>
+        <v>541.46278536</v>
       </c>
       <c r="Q20">
-        <v>1017.08775032</v>
+        <v>1013.16278536</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07045418271069445</v>
+        <v>0.07067940558409887</v>
       </c>
       <c r="T20">
-        <v>0.5693806630645372</v>
+        <v>0.5745821151062094</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.3</v>
       </c>
       <c r="W20">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>13.09359227425064</v>
+        <v>12.04525344961037</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06413971852312009</v>
+        <v>0.06398020722347071</v>
       </c>
       <c r="C21">
-        <v>5114.65662193623</v>
+        <v>5062.652006959392</v>
       </c>
       <c r="D21">
-        <v>6433.92062193623</v>
+        <v>6453.072006959392</v>
       </c>
       <c r="E21">
-        <v>-2196.836</v>
+        <v>-2125.68</v>
       </c>
       <c r="F21">
-        <v>1351.964</v>
+        <v>1423.12</v>
       </c>
       <c r="G21">
         <v>32.7</v>
@@ -3015,28 +3015,28 @@
         <v>843.55</v>
       </c>
       <c r="M21">
-        <v>70.03173520000001</v>
+        <v>73.71761600000001</v>
       </c>
       <c r="N21">
-        <v>773.5182648</v>
+        <v>769.8323839999999</v>
       </c>
       <c r="O21">
-        <v>232.05547944</v>
+        <v>230.9497152</v>
       </c>
       <c r="P21">
-        <v>541.46278536</v>
+        <v>538.8826687999999</v>
       </c>
       <c r="Q21">
-        <v>1013.16278536</v>
+        <v>1010.5826688</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07067940558409887</v>
+        <v>0.07091025902933838</v>
       </c>
       <c r="T21">
-        <v>0.5745821151062094</v>
+        <v>0.5799136034489235</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>12.04525344961037</v>
+        <v>11.44299077712985</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06398020722347071</v>
+        <v>0.06382069592382134</v>
       </c>
       <c r="C22">
-        <v>5062.652006959392</v>
+        <v>5010.761745448674</v>
       </c>
       <c r="D22">
-        <v>6453.072006959392</v>
+        <v>6472.337745448674</v>
       </c>
       <c r="E22">
-        <v>-2125.68</v>
+        <v>-2054.524</v>
       </c>
       <c r="F22">
-        <v>1423.12</v>
+        <v>1494.276</v>
       </c>
       <c r="G22">
         <v>32.7</v>
@@ -3097,28 +3097,28 @@
         <v>843.55</v>
       </c>
       <c r="M22">
-        <v>73.71761600000001</v>
+        <v>77.40349680000001</v>
       </c>
       <c r="N22">
-        <v>769.8323839999999</v>
+        <v>766.1465032</v>
       </c>
       <c r="O22">
-        <v>230.9497152</v>
+        <v>229.84395096</v>
       </c>
       <c r="P22">
-        <v>538.8826687999999</v>
+        <v>536.30255224</v>
       </c>
       <c r="Q22">
-        <v>1010.5826688</v>
+        <v>1008.00255224</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07091025902933838</v>
+        <v>0.07114695686559663</v>
       </c>
       <c r="T22">
-        <v>0.5799136034489235</v>
+        <v>0.5853800661800607</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.44299077712985</v>
+        <v>10.89808645440938</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06382069592382132</v>
+        <v>0.06366118462417196</v>
       </c>
       <c r="C23">
-        <v>5010.761745448675</v>
+        <v>4958.986864682744</v>
       </c>
       <c r="D23">
-        <v>6472.337745448675</v>
+        <v>6491.718864682744</v>
       </c>
       <c r="E23">
-        <v>-2054.524</v>
+        <v>-1983.368</v>
       </c>
       <c r="F23">
-        <v>1494.276</v>
+        <v>1565.432</v>
       </c>
       <c r="G23">
         <v>32.7</v>
@@ -3179,28 +3179,28 @@
         <v>843.55</v>
       </c>
       <c r="M23">
-        <v>77.4034968</v>
+        <v>81.08937760000001</v>
       </c>
       <c r="N23">
-        <v>766.1465032</v>
+        <v>762.4606223999999</v>
       </c>
       <c r="O23">
-        <v>229.84395096</v>
+        <v>228.73818672</v>
       </c>
       <c r="P23">
-        <v>536.30255224</v>
+        <v>533.72243568</v>
       </c>
       <c r="Q23">
-        <v>1008.00255224</v>
+        <v>1005.42243568</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07114695686559662</v>
+        <v>0.07138972387714354</v>
       </c>
       <c r="T23">
-        <v>0.5853800661800606</v>
+        <v>0.5909866946222526</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.89808645440938</v>
+        <v>10.40271888829986</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06366118462417196</v>
+        <v>0.06350167332452258</v>
       </c>
       <c r="C24">
-        <v>4958.986864682744</v>
+        <v>4907.32840428178</v>
       </c>
       <c r="D24">
-        <v>6491.718864682744</v>
+        <v>6511.216404281779</v>
       </c>
       <c r="E24">
-        <v>-1983.368</v>
+        <v>-1912.212</v>
       </c>
       <c r="F24">
-        <v>1565.432</v>
+        <v>1636.588</v>
       </c>
       <c r="G24">
         <v>32.7</v>
@@ -3261,28 +3261,28 @@
         <v>843.55</v>
       </c>
       <c r="M24">
-        <v>81.08937760000001</v>
+        <v>84.77525840000001</v>
       </c>
       <c r="N24">
-        <v>762.4606223999999</v>
+        <v>758.7747416</v>
       </c>
       <c r="O24">
-        <v>228.73818672</v>
+        <v>227.63242248</v>
       </c>
       <c r="P24">
-        <v>533.72243568</v>
+        <v>531.14231912</v>
       </c>
       <c r="Q24">
-        <v>1005.42243568</v>
+        <v>1002.84231912</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07138972387714354</v>
+        <v>0.071638796525354</v>
       </c>
       <c r="T24">
-        <v>0.5909866946222526</v>
+        <v>0.5967389497772287</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.40271888829986</v>
+        <v>9.950426762721609</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06350167332452258</v>
+        <v>0.06362776202487322</v>
       </c>
       <c r="C25">
-        <v>4907.32840428178</v>
+        <v>4820.750532024726</v>
       </c>
       <c r="D25">
-        <v>6511.216404281779</v>
+        <v>6495.794532024726</v>
       </c>
       <c r="E25">
-        <v>-1912.212</v>
+        <v>-1841.056</v>
       </c>
       <c r="F25">
-        <v>1636.588</v>
+        <v>1707.744</v>
       </c>
       <c r="G25">
         <v>32.7</v>
@@ -3343,45 +3343,45 @@
         <v>843.55</v>
       </c>
       <c r="M25">
-        <v>84.77525840000001</v>
+        <v>91.364304</v>
       </c>
       <c r="N25">
-        <v>758.7747416</v>
+        <v>752.185696</v>
       </c>
       <c r="O25">
-        <v>227.63242248</v>
+        <v>225.6557088</v>
       </c>
       <c r="P25">
-        <v>531.14231912</v>
+        <v>526.5299872000001</v>
       </c>
       <c r="Q25">
-        <v>1002.84231912</v>
+        <v>998.2299872000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.071638796525354</v>
+        <v>0.07189442371693844</v>
       </c>
       <c r="T25">
-        <v>0.5967389497772287</v>
+        <v>0.6026425800678623</v>
       </c>
       <c r="U25">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>9.950426762721609</v>
+        <v>9.232818103665519</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06362776202487322</v>
+        <v>0.06348015072522384</v>
       </c>
       <c r="C26">
-        <v>4820.750532024726</v>
+        <v>4767.656146615685</v>
       </c>
       <c r="D26">
-        <v>6495.794532024726</v>
+        <v>6513.856146615686</v>
       </c>
       <c r="E26">
-        <v>-1841.056</v>
+        <v>-1769.9</v>
       </c>
       <c r="F26">
-        <v>1707.744</v>
+        <v>1778.9</v>
       </c>
       <c r="G26">
         <v>32.7</v>
@@ -3425,28 +3425,28 @@
         <v>843.55</v>
       </c>
       <c r="M26">
-        <v>91.36430399999999</v>
+        <v>95.17115</v>
       </c>
       <c r="N26">
-        <v>752.185696</v>
+        <v>748.3788499999999</v>
       </c>
       <c r="O26">
-        <v>225.6557088</v>
+        <v>224.513655</v>
       </c>
       <c r="P26">
-        <v>526.5299872000001</v>
+        <v>523.865195</v>
       </c>
       <c r="Q26">
-        <v>998.2299872000001</v>
+        <v>995.5651949999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07189442371693844</v>
+        <v>0.07215686763363179</v>
       </c>
       <c r="T26">
-        <v>0.6026425800678623</v>
+        <v>0.6087036404995793</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.232818103665521</v>
+        <v>8.863505379518898</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06348015072522384</v>
+        <v>0.06333253942557446</v>
       </c>
       <c r="C27">
-        <v>4767.656146615685</v>
+        <v>4714.662482223021</v>
       </c>
       <c r="D27">
-        <v>6513.856146615686</v>
+        <v>6532.018482223021</v>
       </c>
       <c r="E27">
-        <v>-1769.9</v>
+        <v>-1698.744</v>
       </c>
       <c r="F27">
-        <v>1778.9</v>
+        <v>1850.056</v>
       </c>
       <c r="G27">
         <v>32.7</v>
@@ -3507,28 +3507,28 @@
         <v>843.55</v>
       </c>
       <c r="M27">
-        <v>95.17115</v>
+        <v>98.97799600000002</v>
       </c>
       <c r="N27">
-        <v>748.3788499999999</v>
+        <v>744.5720039999999</v>
       </c>
       <c r="O27">
-        <v>224.513655</v>
+        <v>223.3716012</v>
       </c>
       <c r="P27">
-        <v>523.865195</v>
+        <v>521.2004027999999</v>
       </c>
       <c r="Q27">
-        <v>995.5651949999999</v>
+        <v>992.9004027999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07215686763363179</v>
+        <v>0.07242640462915467</v>
       </c>
       <c r="T27">
-        <v>0.6087036404995793</v>
+        <v>0.6149285133753967</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.863505379518898</v>
+        <v>8.522601326460476</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06333253942557446</v>
+        <v>0.06318492812592509</v>
       </c>
       <c r="C28">
-        <v>4714.662482223021</v>
+        <v>4661.770383712095</v>
       </c>
       <c r="D28">
-        <v>6532.018482223021</v>
+        <v>6550.282383712096</v>
       </c>
       <c r="E28">
-        <v>-1698.744</v>
+        <v>-1627.588</v>
       </c>
       <c r="F28">
-        <v>1850.056</v>
+        <v>1921.212</v>
       </c>
       <c r="G28">
         <v>32.7</v>
@@ -3589,28 +3589,28 @@
         <v>843.55</v>
       </c>
       <c r="M28">
-        <v>98.97799600000002</v>
+        <v>102.784842</v>
       </c>
       <c r="N28">
-        <v>744.5720039999999</v>
+        <v>740.7651579999999</v>
       </c>
       <c r="O28">
-        <v>223.3716012</v>
+        <v>222.2295474</v>
       </c>
       <c r="P28">
-        <v>521.2004027999999</v>
+        <v>518.5356105999999</v>
       </c>
       <c r="Q28">
-        <v>992.9004027999999</v>
+        <v>990.2356106</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07242640462915467</v>
+        <v>0.07270332619989739</v>
       </c>
       <c r="T28">
-        <v>0.6149285133753967</v>
+        <v>0.6213239307135654</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.522601326460476</v>
+        <v>8.20694942548046</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06318492812592509</v>
+        <v>0.06303731682627571</v>
       </c>
       <c r="C29">
-        <v>4661.770383712095</v>
+        <v>4608.980705423937</v>
       </c>
       <c r="D29">
-        <v>6550.282383712096</v>
+        <v>6568.648705423938</v>
       </c>
       <c r="E29">
-        <v>-1627.588</v>
+        <v>-1556.432</v>
       </c>
       <c r="F29">
-        <v>1921.212</v>
+        <v>1992.368</v>
       </c>
       <c r="G29">
         <v>32.7</v>
@@ -3671,28 +3671,28 @@
         <v>843.55</v>
       </c>
       <c r="M29">
-        <v>102.784842</v>
+        <v>106.591688</v>
       </c>
       <c r="N29">
-        <v>740.7651579999999</v>
+        <v>736.958312</v>
       </c>
       <c r="O29">
-        <v>222.2295474</v>
+        <v>221.0874936</v>
       </c>
       <c r="P29">
-        <v>518.5356105999999</v>
+        <v>515.8708184</v>
       </c>
       <c r="Q29">
-        <v>990.2356106</v>
+        <v>987.5708184</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07270332619989739</v>
+        <v>0.07298794003649405</v>
       </c>
       <c r="T29">
-        <v>0.6213239307135654</v>
+        <v>0.6278969985333497</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.20694942548046</v>
+        <v>7.913844088856158</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06303731682627571</v>
+        <v>0.06288970552662634</v>
       </c>
       <c r="C30">
-        <v>4608.980705423937</v>
+        <v>4556.294311308453</v>
       </c>
       <c r="D30">
-        <v>6568.648705423938</v>
+        <v>6587.118311308453</v>
       </c>
       <c r="E30">
-        <v>-1556.432</v>
+        <v>-1485.276</v>
       </c>
       <c r="F30">
-        <v>1992.368</v>
+        <v>2063.524</v>
       </c>
       <c r="G30">
         <v>32.7</v>
@@ -3753,28 +3753,28 @@
         <v>843.55</v>
       </c>
       <c r="M30">
-        <v>106.591688</v>
+        <v>110.398534</v>
       </c>
       <c r="N30">
-        <v>736.958312</v>
+        <v>733.1514659999999</v>
       </c>
       <c r="O30">
-        <v>221.0874936</v>
+        <v>219.9454398</v>
       </c>
       <c r="P30">
-        <v>515.8708184</v>
+        <v>513.2060262</v>
       </c>
       <c r="Q30">
-        <v>987.5708184</v>
+        <v>984.9060262</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07298794003649405</v>
+        <v>0.07328057116426245</v>
       </c>
       <c r="T30">
-        <v>0.6278969985333497</v>
+        <v>0.6346552231931282</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.913844088856158</v>
+        <v>7.640952913378359</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06288970552662634</v>
+        <v>0.06291009422697696</v>
       </c>
       <c r="C31">
-        <v>4556.294311308453</v>
+        <v>4482.581030857784</v>
       </c>
       <c r="D31">
-        <v>6587.118311308453</v>
+        <v>6584.561030857783</v>
       </c>
       <c r="E31">
-        <v>-1485.276</v>
+        <v>-1414.12</v>
       </c>
       <c r="F31">
-        <v>2063.524</v>
+        <v>2134.68</v>
       </c>
       <c r="G31">
         <v>32.7</v>
@@ -3835,45 +3835,45 @@
         <v>843.55</v>
       </c>
       <c r="M31">
-        <v>110.398534</v>
+        <v>115.913124</v>
       </c>
       <c r="N31">
-        <v>733.1514659999999</v>
+        <v>727.6368759999999</v>
       </c>
       <c r="O31">
-        <v>219.9454398</v>
+        <v>218.2910628</v>
       </c>
       <c r="P31">
-        <v>513.2060262</v>
+        <v>509.3458132</v>
       </c>
       <c r="Q31">
-        <v>984.9060262</v>
+        <v>981.0458131999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07328057116426245</v>
+        <v>0.07358156318139566</v>
       </c>
       <c r="T31">
-        <v>0.6346552231931282</v>
+        <v>0.641606539986043</v>
       </c>
       <c r="U31">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V31">
         <v>0.3</v>
       </c>
       <c r="W31">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y31">
-        <v>7.64095291337836</v>
+        <v>7.277433054086265</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06291009422697696</v>
+        <v>0.06276808292732758</v>
       </c>
       <c r="C32">
-        <v>4482.581030857784</v>
+        <v>4429.278352522791</v>
       </c>
       <c r="D32">
-        <v>6584.561030857783</v>
+        <v>6602.414352522791</v>
       </c>
       <c r="E32">
-        <v>-1414.12</v>
+        <v>-1342.964</v>
       </c>
       <c r="F32">
-        <v>2134.68</v>
+        <v>2205.836</v>
       </c>
       <c r="G32">
         <v>32.7</v>
@@ -3917,28 +3917,28 @@
         <v>843.55</v>
       </c>
       <c r="M32">
-        <v>115.913124</v>
+        <v>119.7768948</v>
       </c>
       <c r="N32">
-        <v>727.6368759999999</v>
+        <v>723.7731051999999</v>
       </c>
       <c r="O32">
-        <v>218.2910628</v>
+        <v>217.13193156</v>
       </c>
       <c r="P32">
-        <v>509.3458132</v>
+        <v>506.6411736399999</v>
       </c>
       <c r="Q32">
-        <v>981.0458131999999</v>
+        <v>978.3411736399999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07358156318139566</v>
+        <v>0.07389127960482259</v>
       </c>
       <c r="T32">
-        <v>0.641606539986043</v>
+        <v>0.6487593442222307</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.277433054086265</v>
+        <v>7.042677149115739</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06276808292732758</v>
+        <v>0.06262607162767819</v>
       </c>
       <c r="C33">
-        <v>4429.278352522791</v>
+        <v>4376.07275208698</v>
       </c>
       <c r="D33">
-        <v>6602.414352522791</v>
+        <v>6620.364752086981</v>
       </c>
       <c r="E33">
-        <v>-1342.964</v>
+        <v>-1271.808</v>
       </c>
       <c r="F33">
-        <v>2205.836</v>
+        <v>2276.992</v>
       </c>
       <c r="G33">
         <v>32.7</v>
@@ -3999,28 +3999,28 @@
         <v>843.55</v>
       </c>
       <c r="M33">
-        <v>119.7768948</v>
+        <v>123.6406656</v>
       </c>
       <c r="N33">
-        <v>723.7731051999999</v>
+        <v>719.9093343999999</v>
       </c>
       <c r="O33">
-        <v>217.13193156</v>
+        <v>215.97280032</v>
       </c>
       <c r="P33">
-        <v>506.6411736399999</v>
+        <v>503.9365340799999</v>
       </c>
       <c r="Q33">
-        <v>978.3411736399999</v>
+        <v>975.6365340799999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07389127960482259</v>
+        <v>0.07421010533482089</v>
       </c>
       <c r="T33">
-        <v>0.6487593442222307</v>
+        <v>0.6561225250536005</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.042677149115739</v>
+        <v>6.822593488205873</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06262607162767819</v>
+        <v>0.06248406032802883</v>
       </c>
       <c r="C34">
-        <v>4376.07275208698</v>
+        <v>4322.965023504309</v>
       </c>
       <c r="D34">
-        <v>6620.364752086981</v>
+        <v>6638.413023504309</v>
       </c>
       <c r="E34">
-        <v>-1271.808</v>
+        <v>-1200.652</v>
       </c>
       <c r="F34">
-        <v>2276.992</v>
+        <v>2348.148</v>
       </c>
       <c r="G34">
         <v>32.7</v>
@@ -4081,28 +4081,28 @@
         <v>843.55</v>
       </c>
       <c r="M34">
-        <v>123.6406656</v>
+        <v>127.5044364</v>
       </c>
       <c r="N34">
-        <v>719.9093343999999</v>
+        <v>716.0455635999999</v>
       </c>
       <c r="O34">
-        <v>215.97280032</v>
+        <v>214.81366908</v>
       </c>
       <c r="P34">
-        <v>503.9365340799999</v>
+        <v>501.23189452</v>
       </c>
       <c r="Q34">
-        <v>975.6365340799999</v>
+        <v>972.93189452</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07421010533482089</v>
+        <v>0.07453844825078931</v>
       </c>
       <c r="T34">
-        <v>0.6561225250536005</v>
+        <v>0.6637055023276979</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.822593488205873</v>
+        <v>6.615848230987513</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06248406032802883</v>
+        <v>0.06234204902837946</v>
       </c>
       <c r="C35">
-        <v>4322.965023504309</v>
+        <v>4269.95596941024</v>
       </c>
       <c r="D35">
-        <v>6638.413023504309</v>
+        <v>6656.55996941024</v>
       </c>
       <c r="E35">
-        <v>-1200.652</v>
+        <v>-1129.496</v>
       </c>
       <c r="F35">
-        <v>2348.148</v>
+        <v>2419.304</v>
       </c>
       <c r="G35">
         <v>32.7</v>
@@ -4163,28 +4163,28 @@
         <v>843.55</v>
       </c>
       <c r="M35">
-        <v>127.5044364</v>
+        <v>131.3682072</v>
       </c>
       <c r="N35">
-        <v>716.0455635999999</v>
+        <v>712.1817927999999</v>
       </c>
       <c r="O35">
-        <v>214.81366908</v>
+        <v>213.65453784</v>
       </c>
       <c r="P35">
-        <v>501.23189452</v>
+        <v>498.5272549599999</v>
       </c>
       <c r="Q35">
-        <v>972.93189452</v>
+        <v>970.22725496</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07453844825078931</v>
+        <v>0.0748767409520901</v>
       </c>
       <c r="T35">
-        <v>0.6637055023276979</v>
+        <v>0.6715182667919192</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.615848230987513</v>
+        <v>6.42126445948788</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06234204902837946</v>
+        <v>0.06220003772873008</v>
       </c>
       <c r="C36">
-        <v>4269.95596941024</v>
+        <v>4217.046401240712</v>
       </c>
       <c r="D36">
-        <v>6656.55996941024</v>
+        <v>6674.806401240712</v>
       </c>
       <c r="E36">
-        <v>-1129.496</v>
+        <v>-1058.34</v>
       </c>
       <c r="F36">
-        <v>2419.304</v>
+        <v>2490.46</v>
       </c>
       <c r="G36">
         <v>32.7</v>
@@ -4245,28 +4245,28 @@
         <v>843.55</v>
       </c>
       <c r="M36">
-        <v>131.3682072</v>
+        <v>135.231978</v>
       </c>
       <c r="N36">
-        <v>712.1817927999999</v>
+        <v>708.3180219999999</v>
       </c>
       <c r="O36">
-        <v>213.65453784</v>
+        <v>212.4954066</v>
       </c>
       <c r="P36">
-        <v>498.5272549599999</v>
+        <v>495.8226154</v>
       </c>
       <c r="Q36">
-        <v>970.22725496</v>
+        <v>967.5226153999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.0748767409520901</v>
+        <v>0.07522544265958475</v>
       </c>
       <c r="T36">
-        <v>0.6715182667919192</v>
+        <v>0.6795714240088858</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.42126445948788</v>
+        <v>6.237799760645369</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06220003772873008</v>
+        <v>0.06231002642908072</v>
       </c>
       <c r="C37">
-        <v>4217.046401240712</v>
+        <v>4131.74970134966</v>
       </c>
       <c r="D37">
-        <v>6674.806401240712</v>
+        <v>6660.66570134966</v>
       </c>
       <c r="E37">
-        <v>-1058.34</v>
+        <v>-987.1839999999997</v>
       </c>
       <c r="F37">
-        <v>2490.46</v>
+        <v>2561.616</v>
       </c>
       <c r="G37">
         <v>32.7</v>
@@ -4327,45 +4327,45 @@
         <v>843.55</v>
       </c>
       <c r="M37">
-        <v>135.231978</v>
+        <v>141.6573648</v>
       </c>
       <c r="N37">
-        <v>708.3180219999999</v>
+        <v>701.8926351999999</v>
       </c>
       <c r="O37">
-        <v>212.4954066</v>
+        <v>210.56779056</v>
       </c>
       <c r="P37">
-        <v>495.8226154</v>
+        <v>491.3248446399999</v>
       </c>
       <c r="Q37">
-        <v>967.5226153999999</v>
+        <v>963.0248446399999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07522544265958475</v>
+        <v>0.07558504129543862</v>
       </c>
       <c r="T37">
-        <v>0.6795714240088858</v>
+        <v>0.6878762423888827</v>
       </c>
       <c r="U37">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V37">
         <v>0.3</v>
       </c>
       <c r="W37">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>6.237799760645369</v>
+        <v>5.954861585848162</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06231002642908072</v>
+        <v>0.06217501512943133</v>
       </c>
       <c r="C38">
-        <v>4131.74970134966</v>
+        <v>4077.959819969586</v>
       </c>
       <c r="D38">
-        <v>6660.66570134966</v>
+        <v>6678.031819969586</v>
       </c>
       <c r="E38">
-        <v>-987.1840000000002</v>
+        <v>-916.0280000000002</v>
       </c>
       <c r="F38">
-        <v>2561.616</v>
+        <v>2632.772</v>
       </c>
       <c r="G38">
         <v>32.7</v>
@@ -4409,28 +4409,28 @@
         <v>843.55</v>
       </c>
       <c r="M38">
-        <v>141.6573648</v>
+        <v>145.5922916</v>
       </c>
       <c r="N38">
-        <v>701.8926352</v>
+        <v>697.9577084</v>
       </c>
       <c r="O38">
-        <v>210.56779056</v>
+        <v>209.38731252</v>
       </c>
       <c r="P38">
-        <v>491.32484464</v>
+        <v>488.57039588</v>
       </c>
       <c r="Q38">
-        <v>963.02484464</v>
+        <v>960.27039588</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07558504129543862</v>
+        <v>0.07595605576100212</v>
       </c>
       <c r="T38">
-        <v>0.6878762423888827</v>
+        <v>0.6964447057968158</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.954861585848164</v>
+        <v>5.793919380825241</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06217501512943133</v>
+        <v>0.06204000382978197</v>
       </c>
       <c r="C39">
-        <v>4077.959819969586</v>
+        <v>4024.260731446934</v>
       </c>
       <c r="D39">
-        <v>6678.031819969586</v>
+        <v>6695.488731446934</v>
       </c>
       <c r="E39">
-        <v>-916.0280000000002</v>
+        <v>-844.8719999999998</v>
       </c>
       <c r="F39">
-        <v>2632.772</v>
+        <v>2703.928</v>
       </c>
       <c r="G39">
         <v>32.7</v>
@@ -4491,28 +4491,28 @@
         <v>843.55</v>
       </c>
       <c r="M39">
-        <v>145.5922916</v>
+        <v>149.5272184</v>
       </c>
       <c r="N39">
-        <v>697.9577084</v>
+        <v>694.0227815999999</v>
       </c>
       <c r="O39">
-        <v>209.38731252</v>
+        <v>208.20683448</v>
       </c>
       <c r="P39">
-        <v>488.57039588</v>
+        <v>485.8159471199999</v>
       </c>
       <c r="Q39">
-        <v>960.27039588</v>
+        <v>957.51594712</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.07595605576100212</v>
+        <v>0.07633903843513221</v>
       </c>
       <c r="T39">
-        <v>0.6964447057968158</v>
+        <v>0.7052895712501663</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.793919380825241</v>
+        <v>5.641447818171944</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06204000382978197</v>
+        <v>0.06190499253013259</v>
       </c>
       <c r="C40">
-        <v>4024.260731446934</v>
+        <v>3970.653149667324</v>
       </c>
       <c r="D40">
-        <v>6695.488731446934</v>
+        <v>6713.037149667324</v>
       </c>
       <c r="E40">
-        <v>-844.8719999999998</v>
+        <v>-773.7159999999999</v>
       </c>
       <c r="F40">
-        <v>2703.928</v>
+        <v>2775.084</v>
       </c>
       <c r="G40">
         <v>32.7</v>
@@ -4573,28 +4573,28 @@
         <v>843.55</v>
       </c>
       <c r="M40">
-        <v>149.5272184</v>
+        <v>153.4621452</v>
       </c>
       <c r="N40">
-        <v>694.0227815999999</v>
+        <v>690.0878547999999</v>
       </c>
       <c r="O40">
-        <v>208.20683448</v>
+        <v>207.02635644</v>
       </c>
       <c r="P40">
-        <v>485.8159471199999</v>
+        <v>483.06149836</v>
       </c>
       <c r="Q40">
-        <v>957.51594712</v>
+        <v>954.7614983599999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.07633903843513221</v>
+        <v>0.07673457791825014</v>
       </c>
       <c r="T40">
-        <v>0.7052895712501663</v>
+        <v>0.7144244322921512</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.641447818171944</v>
+        <v>5.49679531001369</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06190499253013259</v>
+        <v>0.06176998123048322</v>
       </c>
       <c r="C41">
-        <v>3970.653149667324</v>
+        <v>3917.13779602022</v>
       </c>
       <c r="D41">
-        <v>6713.037149667324</v>
+        <v>6730.677796020221</v>
       </c>
       <c r="E41">
-        <v>-773.7159999999999</v>
+        <v>-702.5599999999999</v>
       </c>
       <c r="F41">
-        <v>2775.084</v>
+        <v>2846.24</v>
       </c>
       <c r="G41">
         <v>32.7</v>
@@ -4655,28 +4655,28 @@
         <v>843.55</v>
       </c>
       <c r="M41">
-        <v>153.4621452</v>
+        <v>157.397072</v>
       </c>
       <c r="N41">
-        <v>690.0878547999999</v>
+        <v>686.152928</v>
       </c>
       <c r="O41">
-        <v>207.02635644</v>
+        <v>205.8458784</v>
       </c>
       <c r="P41">
-        <v>483.06149836</v>
+        <v>480.3070496</v>
       </c>
       <c r="Q41">
-        <v>954.7614983599999</v>
+        <v>952.0070496000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.07673457791825014</v>
+        <v>0.07714330205080536</v>
       </c>
       <c r="T41">
-        <v>0.7144244322921512</v>
+        <v>0.7238637887022025</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.49679531001369</v>
+        <v>5.359375427263348</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06176998123048322</v>
+        <v>0.06163496993083384</v>
       </c>
       <c r="C42">
-        <v>3917.13779602022</v>
+        <v>3863.715399497789</v>
       </c>
       <c r="D42">
-        <v>6730.677796020221</v>
+        <v>6748.41139949779</v>
       </c>
       <c r="E42">
-        <v>-702.5599999999999</v>
+        <v>-631.404</v>
       </c>
       <c r="F42">
-        <v>2846.24</v>
+        <v>2917.396</v>
       </c>
       <c r="G42">
         <v>32.7</v>
@@ -4737,28 +4737,28 @@
         <v>843.55</v>
       </c>
       <c r="M42">
-        <v>157.397072</v>
+        <v>161.3319988</v>
       </c>
       <c r="N42">
-        <v>686.152928</v>
+        <v>682.2180011999999</v>
       </c>
       <c r="O42">
-        <v>205.8458784</v>
+        <v>204.6654003599999</v>
       </c>
       <c r="P42">
-        <v>480.3070496</v>
+        <v>477.55260084</v>
       </c>
       <c r="Q42">
-        <v>952.0070496000001</v>
+        <v>949.25260084</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.07714330205080536</v>
+        <v>0.07756588123870142</v>
       </c>
       <c r="T42">
-        <v>0.7238637887022025</v>
+        <v>0.7336231232956449</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.359375427263348</v>
+        <v>5.228658953427656</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06163496993083384</v>
+        <v>0.06149995863118447</v>
       </c>
       <c r="C43">
-        <v>3863.715399497789</v>
+        <v>3810.386696795322</v>
       </c>
       <c r="D43">
-        <v>6748.41139949779</v>
+        <v>6766.238696795323</v>
       </c>
       <c r="E43">
-        <v>-631.404</v>
+        <v>-560.2479999999996</v>
       </c>
       <c r="F43">
-        <v>2917.396</v>
+        <v>2988.552000000001</v>
       </c>
       <c r="G43">
         <v>32.7</v>
@@ -4819,28 +4819,28 @@
         <v>843.55</v>
       </c>
       <c r="M43">
-        <v>161.3319988</v>
+        <v>165.2669256</v>
       </c>
       <c r="N43">
-        <v>682.2180011999999</v>
+        <v>678.2830743999999</v>
       </c>
       <c r="O43">
-        <v>204.6654003599999</v>
+        <v>203.48492232</v>
       </c>
       <c r="P43">
-        <v>477.55260084</v>
+        <v>474.7981520799999</v>
       </c>
       <c r="Q43">
-        <v>949.25260084</v>
+        <v>946.49815208</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.07756588123870142</v>
+        <v>0.07800303212273184</v>
       </c>
       <c r="T43">
-        <v>0.7336231232956449</v>
+        <v>0.7437189866681718</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.228658953427656</v>
+        <v>5.10416707358414</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06149995863118447</v>
+        <v>0.06136494733153509</v>
       </c>
       <c r="C44">
-        <v>3810.386696795322</v>
+        <v>3757.152432413247</v>
       </c>
       <c r="D44">
-        <v>6766.238696795323</v>
+        <v>6784.160432413247</v>
       </c>
       <c r="E44">
-        <v>-560.248</v>
+        <v>-489.0920000000001</v>
       </c>
       <c r="F44">
-        <v>2988.552</v>
+        <v>3059.708</v>
       </c>
       <c r="G44">
         <v>32.7</v>
@@ -4901,28 +4901,28 @@
         <v>843.55</v>
       </c>
       <c r="M44">
-        <v>165.2669256</v>
+        <v>169.2018524</v>
       </c>
       <c r="N44">
-        <v>678.2830743999999</v>
+        <v>674.3481475999999</v>
       </c>
       <c r="O44">
-        <v>203.48492232</v>
+        <v>202.30444428</v>
       </c>
       <c r="P44">
-        <v>474.7981520799999</v>
+        <v>472.04370332</v>
       </c>
       <c r="Q44">
-        <v>946.49815208</v>
+        <v>943.7437033199999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.07800303212273182</v>
+        <v>0.07845552163427208</v>
       </c>
       <c r="T44">
-        <v>0.7437189866681717</v>
+        <v>0.7541690908607873</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.104167073584141</v>
+        <v>4.985465513733347</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06136494733153509</v>
+        <v>0.06122993603188571</v>
       </c>
       <c r="C45">
-        <v>3757.152432413247</v>
+        <v>3704.013358760773</v>
       </c>
       <c r="D45">
-        <v>6784.160432413247</v>
+        <v>6802.177358760773</v>
       </c>
       <c r="E45">
-        <v>-489.0920000000001</v>
+        <v>-417.9360000000001</v>
       </c>
       <c r="F45">
-        <v>3059.708</v>
+        <v>3130.864</v>
       </c>
       <c r="G45">
         <v>32.7</v>
@@ -4983,28 +4983,28 @@
         <v>843.55</v>
       </c>
       <c r="M45">
-        <v>169.2018524</v>
+        <v>173.1367792</v>
       </c>
       <c r="N45">
-        <v>674.3481475999999</v>
+        <v>670.4132208</v>
       </c>
       <c r="O45">
-        <v>202.30444428</v>
+        <v>201.12396624</v>
       </c>
       <c r="P45">
-        <v>472.04370332</v>
+        <v>469.28925456</v>
       </c>
       <c r="Q45">
-        <v>943.7437033199999</v>
+        <v>940.9892545600001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.07845552163427208</v>
+        <v>0.0789241714855102</v>
       </c>
       <c r="T45">
-        <v>0.7541690908607873</v>
+        <v>0.764992413060282</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.985465513733347</v>
+        <v>4.872159479330316</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06122993603188571</v>
+        <v>0.06109492473223635</v>
       </c>
       <c r="C46">
-        <v>3704.013358760773</v>
+        <v>3650.970236261187</v>
       </c>
       <c r="D46">
-        <v>6802.177358760773</v>
+        <v>6820.290236261188</v>
       </c>
       <c r="E46">
-        <v>-417.9360000000001</v>
+        <v>-346.7799999999997</v>
       </c>
       <c r="F46">
-        <v>3130.864</v>
+        <v>3202.02</v>
       </c>
       <c r="G46">
         <v>32.7</v>
@@ -5065,28 +5065,28 @@
         <v>843.55</v>
       </c>
       <c r="M46">
-        <v>173.1367792</v>
+        <v>177.071706</v>
       </c>
       <c r="N46">
-        <v>670.4132208</v>
+        <v>666.4782939999999</v>
       </c>
       <c r="O46">
-        <v>201.12396624</v>
+        <v>199.9434882</v>
       </c>
       <c r="P46">
-        <v>469.28925456</v>
+        <v>466.5348058</v>
       </c>
       <c r="Q46">
-        <v>940.9892545600001</v>
+        <v>938.2348058</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.0789241714855102</v>
+        <v>0.07940986314952062</v>
       </c>
       <c r="T46">
-        <v>0.764992413060282</v>
+        <v>0.7762093106124855</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.872159479330316</v>
+        <v>4.763889268678531</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06109492473223635</v>
+        <v>0.06095991343258697</v>
       </c>
       <c r="C47">
-        <v>3650.970236261187</v>
+        <v>3598.023833458845</v>
       </c>
       <c r="D47">
-        <v>6820.290236261188</v>
+        <v>6838.499833458845</v>
       </c>
       <c r="E47">
-        <v>-346.7799999999997</v>
+        <v>-275.6239999999998</v>
       </c>
       <c r="F47">
-        <v>3202.02</v>
+        <v>3273.176</v>
       </c>
       <c r="G47">
         <v>32.7</v>
@@ -5147,28 +5147,28 @@
         <v>843.55</v>
       </c>
       <c r="M47">
-        <v>177.071706</v>
+        <v>181.0066328</v>
       </c>
       <c r="N47">
-        <v>666.4782939999999</v>
+        <v>662.5433671999999</v>
       </c>
       <c r="O47">
-        <v>199.9434882</v>
+        <v>198.76301016</v>
       </c>
       <c r="P47">
-        <v>466.5348058</v>
+        <v>463.78035704</v>
       </c>
       <c r="Q47">
-        <v>938.2348058</v>
+        <v>935.4803570399999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.07940986314952062</v>
+        <v>0.07991354339367956</v>
       </c>
       <c r="T47">
-        <v>0.7762093106124855</v>
+        <v>0.7878416488147707</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.763889268678531</v>
+        <v>4.660326458489867</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06095991343258697</v>
+        <v>0.0608249021329376</v>
       </c>
       <c r="C48">
-        <v>3598.023833458845</v>
+        <v>3545.17492712786</v>
       </c>
       <c r="D48">
-        <v>6838.499833458845</v>
+        <v>6856.80692712786</v>
       </c>
       <c r="E48">
-        <v>-275.6239999999998</v>
+        <v>-204.4679999999998</v>
       </c>
       <c r="F48">
-        <v>3273.176</v>
+        <v>3344.332</v>
       </c>
       <c r="G48">
         <v>32.7</v>
@@ -5229,28 +5229,28 @@
         <v>843.55</v>
       </c>
       <c r="M48">
-        <v>181.0066328</v>
+        <v>184.9415596</v>
       </c>
       <c r="N48">
-        <v>662.5433671999999</v>
+        <v>658.6084403999999</v>
       </c>
       <c r="O48">
-        <v>198.76301016</v>
+        <v>197.58253212</v>
       </c>
       <c r="P48">
-        <v>463.78035704</v>
+        <v>461.02590828</v>
       </c>
       <c r="Q48">
-        <v>935.4803570399999</v>
+        <v>932.7259082799999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.07991354339367956</v>
+        <v>0.0804362304395049</v>
       </c>
       <c r="T48">
-        <v>0.7878416488147707</v>
+        <v>0.7999129431756327</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.660326458489867</v>
+        <v>4.561170576394338</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0608249021329376</v>
+        <v>0.06152989083328822</v>
       </c>
       <c r="C49">
-        <v>3545.17492712786</v>
+        <v>3379.49023759349</v>
       </c>
       <c r="D49">
-        <v>6856.80692712786</v>
+        <v>6762.27823759349</v>
       </c>
       <c r="E49">
-        <v>-204.4679999999998</v>
+        <v>-133.3119999999999</v>
       </c>
       <c r="F49">
-        <v>3344.332</v>
+        <v>3415.488</v>
       </c>
       <c r="G49">
         <v>32.7</v>
@@ -5311,45 +5311,45 @@
         <v>843.55</v>
       </c>
       <c r="M49">
-        <v>184.9415596</v>
+        <v>197.4152064</v>
       </c>
       <c r="N49">
-        <v>658.6084403999999</v>
+        <v>646.1347936</v>
       </c>
       <c r="O49">
-        <v>197.58253212</v>
+        <v>193.84043808</v>
       </c>
       <c r="P49">
-        <v>461.02590828</v>
+        <v>452.29435552</v>
       </c>
       <c r="Q49">
-        <v>932.7259082799999</v>
+        <v>923.99435552</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.0804362304395049</v>
+        <v>0.08097902083324657</v>
       </c>
       <c r="T49">
-        <v>0.7999129431756327</v>
+        <v>0.8124485180888354</v>
       </c>
       <c r="U49">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V49">
         <v>0.3</v>
       </c>
       <c r="W49">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.561170576394338</v>
+        <v>4.272973776350391</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06152989083328822</v>
+        <v>0.06141237953363885</v>
       </c>
       <c r="C50">
-        <v>3379.49023759349</v>
+        <v>3323.909356040127</v>
       </c>
       <c r="D50">
-        <v>6762.27823759349</v>
+        <v>6777.853356040127</v>
       </c>
       <c r="E50">
-        <v>-133.3120000000004</v>
+        <v>-62.15599999999995</v>
       </c>
       <c r="F50">
-        <v>3415.488</v>
+        <v>3486.644</v>
       </c>
       <c r="G50">
         <v>32.7</v>
@@ -5393,28 +5393,28 @@
         <v>843.55</v>
       </c>
       <c r="M50">
-        <v>197.4152064</v>
+        <v>201.5280232</v>
       </c>
       <c r="N50">
-        <v>646.1347936</v>
+        <v>642.0219767999999</v>
       </c>
       <c r="O50">
-        <v>193.84043808</v>
+        <v>192.60659304</v>
       </c>
       <c r="P50">
-        <v>452.29435552</v>
+        <v>449.4153837599999</v>
       </c>
       <c r="Q50">
-        <v>923.99435552</v>
+        <v>921.11538376</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08097902083324657</v>
+        <v>0.08154309712478205</v>
       </c>
       <c r="T50">
-        <v>0.8124485180888354</v>
+        <v>0.825475684175105</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.272973776350391</v>
+        <v>4.18577022989426</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06141237953363885</v>
+        <v>0.06129486823398947</v>
       </c>
       <c r="C51">
-        <v>3323.909356040127</v>
+        <v>3268.400386444456</v>
       </c>
       <c r="D51">
-        <v>6777.853356040127</v>
+        <v>6793.500386444456</v>
       </c>
       <c r="E51">
-        <v>-62.15599999999995</v>
+        <v>9</v>
       </c>
       <c r="F51">
-        <v>3486.644</v>
+        <v>3557.8</v>
       </c>
       <c r="G51">
         <v>32.7</v>
@@ -5475,28 +5475,28 @@
         <v>843.55</v>
       </c>
       <c r="M51">
-        <v>201.5280232</v>
+        <v>205.64084</v>
       </c>
       <c r="N51">
-        <v>642.0219767999999</v>
+        <v>637.9091599999999</v>
       </c>
       <c r="O51">
-        <v>192.60659304</v>
+        <v>191.372748</v>
       </c>
       <c r="P51">
-        <v>449.4153837599999</v>
+        <v>446.5364119999999</v>
       </c>
       <c r="Q51">
-        <v>921.11538376</v>
+        <v>918.236412</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08154309712478205</v>
+        <v>0.08212973646797894</v>
       </c>
       <c r="T51">
-        <v>0.825475684175105</v>
+        <v>0.8390239369048255</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.18577022989426</v>
+        <v>4.102054825296375</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06129486823398947</v>
+        <v>0.0611773569343401</v>
       </c>
       <c r="C52">
-        <v>3268.400386444456</v>
+        <v>3212.963827996473</v>
       </c>
       <c r="D52">
-        <v>6793.500386444456</v>
+        <v>6809.219827996473</v>
       </c>
       <c r="E52">
-        <v>9</v>
+        <v>80.15599999999995</v>
       </c>
       <c r="F52">
-        <v>3557.8</v>
+        <v>3628.956</v>
       </c>
       <c r="G52">
         <v>32.7</v>
@@ -5557,28 +5557,28 @@
         <v>843.55</v>
       </c>
       <c r="M52">
-        <v>205.64084</v>
+        <v>209.7536568</v>
       </c>
       <c r="N52">
-        <v>637.9091599999999</v>
+        <v>633.7963431999999</v>
       </c>
       <c r="O52">
-        <v>191.372748</v>
+        <v>190.13890296</v>
       </c>
       <c r="P52">
-        <v>446.5364119999999</v>
+        <v>443.6574402399999</v>
       </c>
       <c r="Q52">
-        <v>918.236412</v>
+        <v>915.35744024</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08212973646797894</v>
+        <v>0.08274032027416346</v>
       </c>
       <c r="T52">
-        <v>0.8390239369048255</v>
+        <v>0.8531251795418814</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.102054825296375</v>
+        <v>4.021622377741545</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0611773569343401</v>
+        <v>0.06233384563469072</v>
       </c>
       <c r="C53">
-        <v>3212.963827996473</v>
+        <v>2990.19927351783</v>
       </c>
       <c r="D53">
-        <v>6809.219827996473</v>
+        <v>6657.61127351783</v>
       </c>
       <c r="E53">
-        <v>80.15599999999995</v>
+        <v>151.3120000000004</v>
       </c>
       <c r="F53">
-        <v>3628.956</v>
+        <v>3700.112000000001</v>
       </c>
       <c r="G53">
         <v>32.7</v>
@@ -5639,45 +5639,45 @@
         <v>843.55</v>
       </c>
       <c r="M53">
-        <v>209.7536568</v>
+        <v>226.8168656</v>
       </c>
       <c r="N53">
-        <v>633.7963431999999</v>
+        <v>616.7331343999999</v>
       </c>
       <c r="O53">
-        <v>190.13890296</v>
+        <v>185.01994032</v>
       </c>
       <c r="P53">
-        <v>443.6574402399999</v>
+        <v>431.71319408</v>
       </c>
       <c r="Q53">
-        <v>915.35744024</v>
+        <v>903.41319408</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.08274032027416346</v>
+        <v>0.08337634507227235</v>
       </c>
       <c r="T53">
-        <v>0.8531251795418814</v>
+        <v>0.8678139739554812</v>
       </c>
       <c r="U53">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V53">
         <v>0.3</v>
       </c>
       <c r="W53">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>4.021622377741545</v>
+        <v>3.719079697925249</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06233384563469072</v>
+        <v>0.06224083433504134</v>
       </c>
       <c r="C54">
-        <v>2990.19927351783</v>
+        <v>2930.986385079913</v>
       </c>
       <c r="D54">
-        <v>6657.61127351783</v>
+        <v>6669.554385079914</v>
       </c>
       <c r="E54">
-        <v>151.3120000000004</v>
+        <v>222.4680000000003</v>
       </c>
       <c r="F54">
-        <v>3700.112000000001</v>
+        <v>3771.268</v>
       </c>
       <c r="G54">
         <v>32.7</v>
@@ -5721,28 +5721,28 @@
         <v>843.55</v>
       </c>
       <c r="M54">
-        <v>226.8168656</v>
+        <v>231.1787284</v>
       </c>
       <c r="N54">
-        <v>616.7331343999999</v>
+        <v>612.3712715999999</v>
       </c>
       <c r="O54">
-        <v>185.01994032</v>
+        <v>183.71138148</v>
       </c>
       <c r="P54">
-        <v>431.71319408</v>
+        <v>428.6598901199999</v>
       </c>
       <c r="Q54">
-        <v>903.41319408</v>
+        <v>900.3598901199998</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.08337634507227235</v>
+        <v>0.08403943475540712</v>
       </c>
       <c r="T54">
-        <v>0.8678139739554812</v>
+        <v>0.8831278234505109</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.719079697925249</v>
+        <v>3.648908382870056</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06224083433504134</v>
+        <v>0.06214782303539196</v>
       </c>
       <c r="C55">
-        <v>2930.986385079913</v>
+        <v>2871.816423225243</v>
       </c>
       <c r="D55">
-        <v>6669.554385079914</v>
+        <v>6681.540423225244</v>
       </c>
       <c r="E55">
-        <v>222.4680000000003</v>
+        <v>293.6240000000003</v>
       </c>
       <c r="F55">
-        <v>3771.268</v>
+        <v>3842.424</v>
       </c>
       <c r="G55">
         <v>32.7</v>
@@ -5803,28 +5803,28 @@
         <v>843.55</v>
       </c>
       <c r="M55">
-        <v>231.1787284</v>
+        <v>235.5405912</v>
       </c>
       <c r="N55">
-        <v>612.3712715999999</v>
+        <v>608.0094088</v>
       </c>
       <c r="O55">
-        <v>183.71138148</v>
+        <v>182.40282264</v>
       </c>
       <c r="P55">
-        <v>428.6598901199999</v>
+        <v>425.60658616</v>
       </c>
       <c r="Q55">
-        <v>900.3598901199998</v>
+        <v>897.3065861600001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.08403943475540712</v>
+        <v>0.08473135442476515</v>
       </c>
       <c r="T55">
-        <v>0.8831278234505109</v>
+        <v>0.8991074924888027</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.648908382870056</v>
+        <v>3.581336005409499</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06214782303539196</v>
+        <v>0.06205481173574259</v>
       </c>
       <c r="C56">
-        <v>2871.816423225243</v>
+        <v>2812.689619804081</v>
       </c>
       <c r="D56">
-        <v>6681.540423225244</v>
+        <v>6693.569619804081</v>
       </c>
       <c r="E56">
-        <v>293.6240000000003</v>
+        <v>364.7800000000002</v>
       </c>
       <c r="F56">
-        <v>3842.424</v>
+        <v>3913.58</v>
       </c>
       <c r="G56">
         <v>32.7</v>
@@ -5885,28 +5885,28 @@
         <v>843.55</v>
       </c>
       <c r="M56">
-        <v>235.5405912</v>
+        <v>239.902454</v>
       </c>
       <c r="N56">
-        <v>608.0094088</v>
+        <v>603.6475459999999</v>
       </c>
       <c r="O56">
-        <v>182.40282264</v>
+        <v>181.0942638</v>
       </c>
       <c r="P56">
-        <v>425.60658616</v>
+        <v>422.5532822</v>
       </c>
       <c r="Q56">
-        <v>897.3065861600001</v>
+        <v>894.2532821999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.08473135442476515</v>
+        <v>0.08545402607942801</v>
       </c>
       <c r="T56">
-        <v>0.8991074924888027</v>
+        <v>0.9157973690399076</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.581336005409499</v>
+        <v>3.516220805311145</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06205481173574259</v>
+        <v>0.06305940043609322</v>
       </c>
       <c r="C57">
-        <v>2812.689619804081</v>
+        <v>2613.858435361112</v>
       </c>
       <c r="D57">
-        <v>6693.569619804081</v>
+        <v>6565.894435361113</v>
       </c>
       <c r="E57">
-        <v>364.7800000000002</v>
+        <v>435.9360000000006</v>
       </c>
       <c r="F57">
-        <v>3913.58</v>
+        <v>3984.736000000001</v>
       </c>
       <c r="G57">
         <v>32.7</v>
@@ -5967,45 +5967,45 @@
         <v>843.55</v>
       </c>
       <c r="M57">
-        <v>239.902454</v>
+        <v>255.4215776000001</v>
       </c>
       <c r="N57">
-        <v>603.6475459999999</v>
+        <v>588.1284223999999</v>
       </c>
       <c r="O57">
-        <v>181.0942638</v>
+        <v>176.4385267199999</v>
       </c>
       <c r="P57">
-        <v>422.5532822</v>
+        <v>411.6898956799999</v>
       </c>
       <c r="Q57">
-        <v>894.2532821999999</v>
+        <v>883.3898956799999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.08545402607942801</v>
+        <v>0.08620954644566642</v>
       </c>
       <c r="T57">
-        <v>0.9157973690399076</v>
+        <v>0.9332458763433353</v>
       </c>
       <c r="U57">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V57">
         <v>0.3</v>
       </c>
       <c r="W57">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>3.516220805311145</v>
+        <v>3.302579241449332</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06305940043609322</v>
+        <v>0.06298598913644385</v>
       </c>
       <c r="C58">
-        <v>2613.858435361112</v>
+        <v>2551.867235588443</v>
       </c>
       <c r="D58">
-        <v>6565.894435361113</v>
+        <v>6575.059235588444</v>
       </c>
       <c r="E58">
-        <v>435.9360000000006</v>
+        <v>507.0920000000006</v>
       </c>
       <c r="F58">
-        <v>3984.736000000001</v>
+        <v>4055.892000000001</v>
       </c>
       <c r="G58">
         <v>32.7</v>
@@ -6049,28 +6049,28 @@
         <v>843.55</v>
       </c>
       <c r="M58">
-        <v>255.4215776000001</v>
+        <v>259.9826772000001</v>
       </c>
       <c r="N58">
-        <v>588.1284223999999</v>
+        <v>583.5673227999998</v>
       </c>
       <c r="O58">
-        <v>176.4385267199999</v>
+        <v>175.0701968399999</v>
       </c>
       <c r="P58">
-        <v>411.6898956799999</v>
+        <v>408.4971259599999</v>
       </c>
       <c r="Q58">
-        <v>883.3898956799999</v>
+        <v>880.1971259599999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.08620954644566642</v>
+        <v>0.08700020729405547</v>
       </c>
       <c r="T58">
-        <v>0.9332458763433353</v>
+        <v>0.9515059421259923</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.302579241449332</v>
+        <v>3.244639254757238</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06298598913644385</v>
+        <v>0.06291257783679446</v>
       </c>
       <c r="C59">
-        <v>2551.867235588443</v>
+        <v>2489.901656382086</v>
       </c>
       <c r="D59">
-        <v>6575.059235588444</v>
+        <v>6584.249656382087</v>
       </c>
       <c r="E59">
-        <v>507.0920000000006</v>
+        <v>578.2480000000005</v>
       </c>
       <c r="F59">
-        <v>4055.892000000001</v>
+        <v>4127.048000000001</v>
       </c>
       <c r="G59">
         <v>32.7</v>
@@ -6131,28 +6131,28 @@
         <v>843.55</v>
       </c>
       <c r="M59">
-        <v>259.9826772000001</v>
+        <v>264.5437768</v>
       </c>
       <c r="N59">
-        <v>583.5673227999998</v>
+        <v>579.0062231999999</v>
       </c>
       <c r="O59">
-        <v>175.0701968399999</v>
+        <v>173.70186696</v>
       </c>
       <c r="P59">
-        <v>408.4971259599999</v>
+        <v>405.3043562399999</v>
       </c>
       <c r="Q59">
-        <v>880.1971259599999</v>
+        <v>877.0043562399999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.08700020729405547</v>
+        <v>0.08782851865903446</v>
       </c>
       <c r="T59">
-        <v>0.9515059421259923</v>
+        <v>0.9706355348506805</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.244639254757238</v>
+        <v>3.188697198640735</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.06291257783679448</v>
+        <v>0.06283916653714509</v>
       </c>
       <c r="C60">
-        <v>2489.901656382085</v>
+        <v>2427.961805327402</v>
       </c>
       <c r="D60">
-        <v>6584.249656382085</v>
+        <v>6593.465805327402</v>
       </c>
       <c r="E60">
-        <v>578.2479999999996</v>
+        <v>649.4039999999995</v>
       </c>
       <c r="F60">
-        <v>4127.048</v>
+        <v>4198.204</v>
       </c>
       <c r="G60">
         <v>32.7</v>
@@ -6213,28 +6213,28 @@
         <v>843.55</v>
       </c>
       <c r="M60">
-        <v>264.5437768</v>
+        <v>269.1048764</v>
       </c>
       <c r="N60">
-        <v>579.0062232</v>
+        <v>574.4451236</v>
       </c>
       <c r="O60">
-        <v>173.70186696</v>
+        <v>172.33353708</v>
       </c>
       <c r="P60">
-        <v>405.3043562400001</v>
+        <v>402.11158652</v>
       </c>
       <c r="Q60">
-        <v>877.0043562400001</v>
+        <v>873.81158652</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.08782851865903446</v>
+        <v>0.08869723545645145</v>
       </c>
       <c r="T60">
-        <v>0.9706355348506803</v>
+        <v>0.9906982784399874</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.188697198640736</v>
+        <v>3.134651483409536</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.06283916653714509</v>
+        <v>0.06276575523749572</v>
       </c>
       <c r="C61">
-        <v>2427.961805327402</v>
+        <v>2366.047790612953</v>
       </c>
       <c r="D61">
-        <v>6593.465805327402</v>
+        <v>6602.707790612953</v>
       </c>
       <c r="E61">
-        <v>649.4039999999995</v>
+        <v>720.5599999999995</v>
       </c>
       <c r="F61">
-        <v>4198.204</v>
+        <v>4269.36</v>
       </c>
       <c r="G61">
         <v>32.7</v>
@@ -6295,28 +6295,28 @@
         <v>843.55</v>
       </c>
       <c r="M61">
-        <v>269.1048764</v>
+        <v>273.665976</v>
       </c>
       <c r="N61">
-        <v>574.4451236</v>
+        <v>569.884024</v>
       </c>
       <c r="O61">
-        <v>172.33353708</v>
+        <v>170.9652072</v>
       </c>
       <c r="P61">
-        <v>402.11158652</v>
+        <v>398.9188167999999</v>
       </c>
       <c r="Q61">
-        <v>873.81158652</v>
+        <v>870.6188167999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.08869723545645145</v>
+        <v>0.08960938809373931</v>
       </c>
       <c r="T61">
-        <v>0.9906982784399874</v>
+        <v>1.01176415920876</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.134651483409536</v>
+        <v>3.082407292019377</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.06276575523749572</v>
+        <v>0.06269234393784634</v>
       </c>
       <c r="C62">
-        <v>2366.047790612953</v>
+        <v>2304.159721034743</v>
       </c>
       <c r="D62">
-        <v>6602.707790612953</v>
+        <v>6611.975721034743</v>
       </c>
       <c r="E62">
-        <v>720.5599999999995</v>
+        <v>791.7160000000003</v>
       </c>
       <c r="F62">
-        <v>4269.36</v>
+        <v>4340.516000000001</v>
       </c>
       <c r="G62">
         <v>32.7</v>
@@ -6377,28 +6377,28 @@
         <v>843.55</v>
       </c>
       <c r="M62">
-        <v>273.665976</v>
+        <v>278.2270756</v>
       </c>
       <c r="N62">
-        <v>569.884024</v>
+        <v>565.3229243999999</v>
       </c>
       <c r="O62">
-        <v>170.9652072</v>
+        <v>169.59687732</v>
       </c>
       <c r="P62">
-        <v>398.9188167999999</v>
+        <v>395.7260470799999</v>
       </c>
       <c r="Q62">
-        <v>870.6188167999999</v>
+        <v>867.42604708</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.08960938809373931</v>
+        <v>0.09056831778934961</v>
       </c>
       <c r="T62">
-        <v>1.01176415920876</v>
+        <v>1.033910341555418</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.082407292019377</v>
+        <v>3.031876024937092</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.06269234393784634</v>
+        <v>0.06600413263819696</v>
       </c>
       <c r="C63">
-        <v>2304.159721034743</v>
+        <v>1839.248340379645</v>
       </c>
       <c r="D63">
-        <v>6611.975721034743</v>
+        <v>6218.220340379646</v>
       </c>
       <c r="E63">
-        <v>791.7160000000003</v>
+        <v>862.8720000000003</v>
       </c>
       <c r="F63">
-        <v>4340.516000000001</v>
+        <v>4411.672</v>
       </c>
       <c r="G63">
         <v>32.7</v>
@@ -6459,45 +6459,45 @@
         <v>843.55</v>
       </c>
       <c r="M63">
-        <v>278.2270756</v>
+        <v>317.1992168</v>
       </c>
       <c r="N63">
-        <v>565.3229243999999</v>
+        <v>526.3507831999999</v>
       </c>
       <c r="O63">
-        <v>169.59687732</v>
+        <v>157.90523496</v>
       </c>
       <c r="P63">
-        <v>395.7260470799999</v>
+        <v>368.4455482399999</v>
       </c>
       <c r="Q63">
-        <v>867.42604708</v>
+        <v>840.1455482399999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.09056831778934961</v>
+        <v>0.09157771746893939</v>
       </c>
       <c r="T63">
-        <v>1.033910341555418</v>
+        <v>1.057222112446637</v>
       </c>
       <c r="U63">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V63">
         <v>0.3</v>
       </c>
       <c r="W63">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y63">
-        <v>3.031876024937092</v>
+        <v>2.659369744068043</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.06600413263819696</v>
+        <v>0.06598532133854759</v>
       </c>
       <c r="C64">
-        <v>1839.248340379645</v>
+        <v>1770.196431140296</v>
       </c>
       <c r="D64">
-        <v>6218.220340379646</v>
+        <v>6220.324431140297</v>
       </c>
       <c r="E64">
-        <v>862.8720000000003</v>
+        <v>934.0280000000002</v>
       </c>
       <c r="F64">
-        <v>4411.672</v>
+        <v>4482.828</v>
       </c>
       <c r="G64">
         <v>32.7</v>
@@ -6541,28 +6541,28 @@
         <v>843.55</v>
       </c>
       <c r="M64">
-        <v>317.1992168</v>
+        <v>322.3153332000001</v>
       </c>
       <c r="N64">
-        <v>526.3507831999999</v>
+        <v>521.2346667999999</v>
       </c>
       <c r="O64">
-        <v>157.90523496</v>
+        <v>156.37040004</v>
       </c>
       <c r="P64">
-        <v>368.4455482399999</v>
+        <v>364.86426676</v>
       </c>
       <c r="Q64">
-        <v>840.1455482399999</v>
+        <v>836.56426676</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.09157771746893939</v>
+        <v>0.09264167929337189</v>
       </c>
       <c r="T64">
-        <v>1.057222112446637</v>
+        <v>1.081793979061707</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.659369744068043</v>
+        <v>2.617157525908233</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.06598532133854759</v>
+        <v>0.06596651003889822</v>
       </c>
       <c r="C65">
-        <v>1770.196431140296</v>
+        <v>1701.145946326665</v>
       </c>
       <c r="D65">
-        <v>6220.324431140297</v>
+        <v>6222.429946326665</v>
       </c>
       <c r="E65">
-        <v>934.0280000000002</v>
+        <v>1005.184</v>
       </c>
       <c r="F65">
-        <v>4482.828</v>
+        <v>4553.984</v>
       </c>
       <c r="G65">
         <v>32.7</v>
@@ -6623,28 +6623,28 @@
         <v>843.55</v>
       </c>
       <c r="M65">
-        <v>322.3153332000001</v>
+        <v>327.4314496000001</v>
       </c>
       <c r="N65">
-        <v>521.2346667999999</v>
+        <v>516.1185503999999</v>
       </c>
       <c r="O65">
-        <v>156.37040004</v>
+        <v>154.83556512</v>
       </c>
       <c r="P65">
-        <v>364.86426676</v>
+        <v>361.2829852799999</v>
       </c>
       <c r="Q65">
-        <v>836.56426676</v>
+        <v>832.9829852799999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.09264167929337189</v>
+        <v>0.09376475010805063</v>
       </c>
       <c r="T65">
-        <v>1.081793979061707</v>
+        <v>1.107730949377613</v>
       </c>
       <c r="U65">
         <v>0.07190000000000001</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.617157525908233</v>
+        <v>2.576264439565917</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.06596651003889822</v>
+        <v>0.06594769873924886</v>
       </c>
       <c r="C66">
-        <v>1701.145946326665</v>
+        <v>1632.096887385703</v>
       </c>
       <c r="D66">
-        <v>6222.429946326665</v>
+        <v>6224.536887385703</v>
       </c>
       <c r="E66">
-        <v>1005.184</v>
+        <v>1076.34</v>
       </c>
       <c r="F66">
-        <v>4553.984</v>
+        <v>4625.14</v>
       </c>
       <c r="G66">
         <v>32.7</v>
@@ -6705,28 +6705,28 @@
         <v>843.55</v>
       </c>
       <c r="M66">
-        <v>327.4314496000001</v>
+        <v>332.5475660000001</v>
       </c>
       <c r="N66">
-        <v>516.1185503999999</v>
+        <v>511.0024339999999</v>
       </c>
       <c r="O66">
-        <v>154.83556512</v>
+        <v>153.3007301999999</v>
       </c>
       <c r="P66">
-        <v>361.2829852799999</v>
+        <v>357.7017037999999</v>
       </c>
       <c r="Q66">
-        <v>832.9829852799999</v>
+        <v>829.4017038</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.09376475010805063</v>
+        <v>0.09495199639785386</v>
       </c>
       <c r="T66">
-        <v>1.107730949377613</v>
+        <v>1.135150032282999</v>
       </c>
       <c r="U66">
         <v>0.07190000000000001</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.576264439565917</v>
+        <v>2.536629602034133</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.06594769873924886</v>
+        <v>0.06773068743959948</v>
       </c>
       <c r="C67">
-        <v>1632.096887385703</v>
+        <v>1367.383387355305</v>
       </c>
       <c r="D67">
-        <v>6224.536887385703</v>
+        <v>6030.979387355305</v>
       </c>
       <c r="E67">
-        <v>1076.34</v>
+        <v>1147.496</v>
       </c>
       <c r="F67">
-        <v>4625.14</v>
+        <v>4696.296</v>
       </c>
       <c r="G67">
         <v>32.7</v>
@@ -6787,45 +6787,45 @@
         <v>843.55</v>
       </c>
       <c r="M67">
-        <v>332.5475660000001</v>
+        <v>355.9792368</v>
       </c>
       <c r="N67">
-        <v>511.0024339999999</v>
+        <v>487.5707631999999</v>
       </c>
       <c r="O67">
-        <v>153.3007301999999</v>
+        <v>146.27122896</v>
       </c>
       <c r="P67">
-        <v>357.7017037999999</v>
+        <v>341.29953424</v>
       </c>
       <c r="Q67">
-        <v>829.4017038</v>
+        <v>812.99953424</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.09495199639785386</v>
+        <v>0.09620908070470435</v>
       </c>
       <c r="T67">
-        <v>1.135150032282999</v>
+        <v>1.164182002418114</v>
       </c>
       <c r="U67">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V67">
         <v>0.3</v>
       </c>
       <c r="W67">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.536629602034133</v>
+        <v>2.369660679041042</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.06773068743959948</v>
+        <v>0.06773917613995011</v>
       </c>
       <c r="C68">
-        <v>1367.383387355305</v>
+        <v>1295.334659419504</v>
       </c>
       <c r="D68">
-        <v>6030.979387355305</v>
+        <v>6030.086659419504</v>
       </c>
       <c r="E68">
-        <v>1147.496</v>
+        <v>1218.652</v>
       </c>
       <c r="F68">
-        <v>4696.296</v>
+        <v>4767.452</v>
       </c>
       <c r="G68">
         <v>32.7</v>
@@ -6869,28 +6869,28 @@
         <v>843.55</v>
       </c>
       <c r="M68">
-        <v>355.9792368</v>
+        <v>361.3728616</v>
       </c>
       <c r="N68">
-        <v>487.5707631999999</v>
+        <v>482.1771383999999</v>
       </c>
       <c r="O68">
-        <v>146.27122896</v>
+        <v>144.65314152</v>
       </c>
       <c r="P68">
-        <v>341.29953424</v>
+        <v>337.52399688</v>
       </c>
       <c r="Q68">
-        <v>812.99953424</v>
+        <v>809.22399688</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.09620908070470435</v>
+        <v>0.09754235193924274</v>
       </c>
       <c r="T68">
-        <v>1.164182002418114</v>
+        <v>1.194973485894751</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.369660679041042</v>
+        <v>2.334292609204609</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.06773917613995011</v>
+        <v>0.06774766484030073</v>
       </c>
       <c r="C69">
-        <v>1295.334659419504</v>
+        <v>1223.286195734388</v>
       </c>
       <c r="D69">
-        <v>6030.086659419504</v>
+        <v>6029.194195734388</v>
       </c>
       <c r="E69">
-        <v>1218.652</v>
+        <v>1289.808</v>
       </c>
       <c r="F69">
-        <v>4767.452</v>
+        <v>4838.608</v>
       </c>
       <c r="G69">
         <v>32.7</v>
@@ -6951,28 +6951,28 @@
         <v>843.55</v>
       </c>
       <c r="M69">
-        <v>361.3728616</v>
+        <v>366.7664864</v>
       </c>
       <c r="N69">
-        <v>482.1771383999999</v>
+        <v>476.7835135999999</v>
       </c>
       <c r="O69">
-        <v>144.65314152</v>
+        <v>143.03505408</v>
       </c>
       <c r="P69">
-        <v>337.52399688</v>
+        <v>333.74845952</v>
       </c>
       <c r="Q69">
-        <v>809.22399688</v>
+        <v>805.4484595199999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.09754235193924274</v>
+        <v>0.09895895262593979</v>
       </c>
       <c r="T69">
-        <v>1.194973485894751</v>
+        <v>1.227689437088679</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.334292609204609</v>
+        <v>2.299964776716306</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.06774766484030073</v>
+        <v>0.06775615354065136</v>
       </c>
       <c r="C70">
-        <v>1223.286195734388</v>
+        <v>1151.237996182644</v>
       </c>
       <c r="D70">
-        <v>6029.194195734388</v>
+        <v>6028.301996182645</v>
       </c>
       <c r="E70">
-        <v>1289.808</v>
+        <v>1360.964000000001</v>
       </c>
       <c r="F70">
-        <v>4838.608</v>
+        <v>4909.764000000001</v>
       </c>
       <c r="G70">
         <v>32.7</v>
@@ -7033,28 +7033,28 @@
         <v>843.55</v>
       </c>
       <c r="M70">
-        <v>366.7664864</v>
+        <v>372.1601112000001</v>
       </c>
       <c r="N70">
-        <v>476.7835135999999</v>
+        <v>471.3898887999998</v>
       </c>
       <c r="O70">
-        <v>143.03505408</v>
+        <v>141.4169666399999</v>
       </c>
       <c r="P70">
-        <v>333.74845952</v>
+        <v>329.9729221599999</v>
       </c>
       <c r="Q70">
-        <v>805.4484595199999</v>
+        <v>801.6729221599999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.09895895262593979</v>
+        <v>0.100466946905327</v>
       </c>
       <c r="T70">
-        <v>1.227689437088679</v>
+        <v>1.262516094811246</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.299964776716306</v>
+        <v>2.266631953865344</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.06775615354065136</v>
+        <v>0.06776464224100198</v>
       </c>
       <c r="C71">
-        <v>1151.237996182644</v>
+        <v>1079.190060647031</v>
       </c>
       <c r="D71">
-        <v>6028.301996182645</v>
+        <v>6027.410060647032</v>
       </c>
       <c r="E71">
-        <v>1360.964000000001</v>
+        <v>1432.120000000001</v>
       </c>
       <c r="F71">
-        <v>4909.764000000001</v>
+        <v>4980.920000000001</v>
       </c>
       <c r="G71">
         <v>32.7</v>
@@ -7115,28 +7115,28 @@
         <v>843.55</v>
       </c>
       <c r="M71">
-        <v>372.1601112000001</v>
+        <v>377.5537360000001</v>
       </c>
       <c r="N71">
-        <v>471.3898887999998</v>
+        <v>465.9962639999998</v>
       </c>
       <c r="O71">
-        <v>141.4169666399999</v>
+        <v>139.7988791999999</v>
       </c>
       <c r="P71">
-        <v>329.9729221599999</v>
+        <v>326.1973847999999</v>
       </c>
       <c r="Q71">
-        <v>801.6729221599999</v>
+        <v>797.8973847999998</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.100466946905327</v>
+        <v>0.1020754741366733</v>
       </c>
       <c r="T71">
-        <v>1.262516094811246</v>
+        <v>1.299664529715318</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.266631953865344</v>
+        <v>2.234251497381553</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.06776464224100198</v>
+        <v>0.06777313094135261</v>
       </c>
       <c r="C72">
-        <v>1079.190060647031</v>
+        <v>1007.142389010377</v>
       </c>
       <c r="D72">
-        <v>6027.410060647032</v>
+        <v>6026.518389010378</v>
       </c>
       <c r="E72">
-        <v>1432.120000000001</v>
+        <v>1503.276000000001</v>
       </c>
       <c r="F72">
-        <v>4980.920000000001</v>
+        <v>5052.076000000001</v>
       </c>
       <c r="G72">
         <v>32.7</v>
@@ -7197,28 +7197,28 @@
         <v>843.55</v>
       </c>
       <c r="M72">
-        <v>377.5537360000001</v>
+        <v>382.9473608000001</v>
       </c>
       <c r="N72">
-        <v>465.9962639999998</v>
+        <v>460.6026391999998</v>
       </c>
       <c r="O72">
-        <v>139.7988791999999</v>
+        <v>138.1807917599999</v>
       </c>
       <c r="P72">
-        <v>326.1973847999999</v>
+        <v>322.4218474399999</v>
       </c>
       <c r="Q72">
-        <v>797.8973847999998</v>
+        <v>794.1218474399998</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1020754741366733</v>
+        <v>0.1037949342805262</v>
       </c>
       <c r="T72">
-        <v>1.299664529715318</v>
+        <v>1.339374925647257</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.234251497381553</v>
+        <v>2.202783166432517</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.06777313094135261</v>
+        <v>0.06778161964170323</v>
       </c>
       <c r="C73">
-        <v>1007.142389010378</v>
+        <v>935.0949811555802</v>
       </c>
       <c r="D73">
-        <v>6026.518389010378</v>
+        <v>6025.62698115558</v>
       </c>
       <c r="E73">
-        <v>1503.276</v>
+        <v>1574.432</v>
       </c>
       <c r="F73">
-        <v>5052.076</v>
+        <v>5123.232</v>
       </c>
       <c r="G73">
         <v>32.7</v>
@@ -7279,28 +7279,28 @@
         <v>843.55</v>
       </c>
       <c r="M73">
-        <v>382.9473608</v>
+        <v>388.3409856</v>
       </c>
       <c r="N73">
-        <v>460.6026391999999</v>
+        <v>455.2090143999999</v>
       </c>
       <c r="O73">
-        <v>138.18079176</v>
+        <v>136.56270432</v>
       </c>
       <c r="P73">
-        <v>322.42184744</v>
+        <v>318.64631008</v>
       </c>
       <c r="Q73">
-        <v>794.12184744</v>
+        <v>790.34631008</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1037949342805262</v>
+        <v>0.105637213006083</v>
       </c>
       <c r="T73">
-        <v>1.339374925647257</v>
+        <v>1.381921778431477</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.202783166432518</v>
+        <v>2.172188955787622</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.06778161964170323</v>
+        <v>0.06779010834205385</v>
       </c>
       <c r="C74">
-        <v>935.0949811555802</v>
+        <v>863.0478369656039</v>
       </c>
       <c r="D74">
-        <v>6025.62698115558</v>
+        <v>6024.735836965604</v>
       </c>
       <c r="E74">
-        <v>1574.432</v>
+        <v>1645.588</v>
       </c>
       <c r="F74">
-        <v>5123.232</v>
+        <v>5194.388</v>
       </c>
       <c r="G74">
         <v>32.7</v>
@@ -7361,28 +7361,28 @@
         <v>843.55</v>
       </c>
       <c r="M74">
-        <v>388.3409856</v>
+        <v>393.7346104</v>
       </c>
       <c r="N74">
-        <v>455.2090143999999</v>
+        <v>449.8153895999999</v>
       </c>
       <c r="O74">
-        <v>136.56270432</v>
+        <v>134.94461688</v>
       </c>
       <c r="P74">
-        <v>318.64631008</v>
+        <v>314.87077272</v>
       </c>
       <c r="Q74">
-        <v>790.34631008</v>
+        <v>786.5707727199999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.105637213006083</v>
+        <v>0.1076159568224217</v>
       </c>
       <c r="T74">
-        <v>1.381921778431477</v>
+        <v>1.427620249940454</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.172188955787622</v>
+        <v>2.142432942694641</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.06779010834205385</v>
+        <v>0.06779859704240448</v>
       </c>
       <c r="C75">
-        <v>863.0478369656039</v>
+        <v>791.0009563234826</v>
       </c>
       <c r="D75">
-        <v>6024.735836965604</v>
+        <v>6023.844956323483</v>
       </c>
       <c r="E75">
-        <v>1645.588</v>
+        <v>1716.744</v>
       </c>
       <c r="F75">
-        <v>5194.388</v>
+        <v>5265.544</v>
       </c>
       <c r="G75">
         <v>32.7</v>
@@ -7443,28 +7443,28 @@
         <v>843.55</v>
       </c>
       <c r="M75">
-        <v>393.7346104</v>
+        <v>399.1282352</v>
       </c>
       <c r="N75">
-        <v>449.8153895999999</v>
+        <v>444.4217647999999</v>
       </c>
       <c r="O75">
-        <v>134.94461688</v>
+        <v>133.32652944</v>
       </c>
       <c r="P75">
-        <v>314.87077272</v>
+        <v>311.0952353599999</v>
       </c>
       <c r="Q75">
-        <v>786.5707727199999</v>
+        <v>782.7952353599999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1076159568224217</v>
+        <v>0.1097469117015557</v>
       </c>
       <c r="T75">
-        <v>1.427620249940454</v>
+        <v>1.476833988488584</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.142432942694641</v>
+        <v>2.11348114617174</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.06779859704240448</v>
+        <v>0.06780708574275511</v>
       </c>
       <c r="C76">
-        <v>791.0009563234826</v>
+        <v>718.9543391123216</v>
       </c>
       <c r="D76">
-        <v>6023.844956323483</v>
+        <v>6022.954339112322</v>
       </c>
       <c r="E76">
-        <v>1716.744</v>
+        <v>1787.900000000001</v>
       </c>
       <c r="F76">
-        <v>5265.544</v>
+        <v>5336.700000000001</v>
       </c>
       <c r="G76">
         <v>32.7</v>
@@ -7525,28 +7525,28 @@
         <v>843.55</v>
       </c>
       <c r="M76">
-        <v>399.1282352</v>
+        <v>404.5218600000001</v>
       </c>
       <c r="N76">
-        <v>444.4217647999999</v>
+        <v>439.0281399999999</v>
       </c>
       <c r="O76">
-        <v>133.32652944</v>
+        <v>131.708442</v>
       </c>
       <c r="P76">
-        <v>311.0952353599999</v>
+        <v>307.3196979999999</v>
       </c>
       <c r="Q76">
-        <v>782.7952353599999</v>
+        <v>779.0196979999998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1097469117015557</v>
+        <v>0.1120483429710204</v>
       </c>
       <c r="T76">
-        <v>1.476833988488584</v>
+        <v>1.529984826120564</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.11348114617174</v>
+        <v>2.085301397556117</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.06780708574275511</v>
+        <v>0.06781557444310574</v>
       </c>
       <c r="C77">
-        <v>718.9543391123216</v>
+        <v>646.9079852152963</v>
       </c>
       <c r="D77">
-        <v>6022.954339112322</v>
+        <v>6022.063985215297</v>
       </c>
       <c r="E77">
-        <v>1787.900000000001</v>
+        <v>1859.056</v>
       </c>
       <c r="F77">
-        <v>5336.700000000001</v>
+        <v>5407.856000000001</v>
       </c>
       <c r="G77">
         <v>32.7</v>
@@ -7607,28 +7607,28 @@
         <v>843.55</v>
       </c>
       <c r="M77">
-        <v>404.5218600000001</v>
+        <v>409.9154848000001</v>
       </c>
       <c r="N77">
-        <v>439.0281399999999</v>
+        <v>433.6345151999999</v>
       </c>
       <c r="O77">
-        <v>131.708442</v>
+        <v>130.09035456</v>
       </c>
       <c r="P77">
-        <v>307.3196979999999</v>
+        <v>303.54416064</v>
       </c>
       <c r="Q77">
-        <v>779.0196979999998</v>
+        <v>775.24416064</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1120483429710204</v>
+        <v>0.1145415601796072</v>
       </c>
       <c r="T77">
-        <v>1.529984826120564</v>
+        <v>1.587564900221876</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.085301397556117</v>
+        <v>2.057863221272484</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.06781557444310574</v>
+        <v>0.06782406314345636</v>
       </c>
       <c r="C78">
-        <v>646.9079852152963</v>
+        <v>574.8618945156486</v>
       </c>
       <c r="D78">
-        <v>6022.063985215297</v>
+        <v>6021.173894515649</v>
       </c>
       <c r="E78">
-        <v>1859.056</v>
+        <v>1930.212</v>
       </c>
       <c r="F78">
-        <v>5407.856000000001</v>
+        <v>5479.012000000001</v>
       </c>
       <c r="G78">
         <v>32.7</v>
@@ -7689,28 +7689,28 @@
         <v>843.55</v>
       </c>
       <c r="M78">
-        <v>409.9154848000001</v>
+        <v>415.3091096000001</v>
       </c>
       <c r="N78">
-        <v>433.6345151999999</v>
+        <v>428.2408903999999</v>
       </c>
       <c r="O78">
-        <v>130.09035456</v>
+        <v>128.47226712</v>
       </c>
       <c r="P78">
-        <v>303.54416064</v>
+        <v>299.7686232799999</v>
       </c>
       <c r="Q78">
-        <v>775.24416064</v>
+        <v>771.46862328</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1145415601796072</v>
+        <v>0.1172515788845929</v>
       </c>
       <c r="T78">
-        <v>1.587564900221876</v>
+        <v>1.650151937288519</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.057863221272484</v>
+        <v>2.031137724892321</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.06782406314345636</v>
+        <v>0.06783255184380699</v>
       </c>
       <c r="C79">
-        <v>574.8618945156486</v>
+        <v>502.8160668966902</v>
       </c>
       <c r="D79">
-        <v>6021.173894515649</v>
+        <v>6020.284066896691</v>
       </c>
       <c r="E79">
-        <v>1930.212</v>
+        <v>2001.368</v>
       </c>
       <c r="F79">
-        <v>5479.012000000001</v>
+        <v>5550.168000000001</v>
       </c>
       <c r="G79">
         <v>32.7</v>
@@ -7771,28 +7771,28 @@
         <v>843.55</v>
       </c>
       <c r="M79">
-        <v>415.3091096000001</v>
+        <v>420.7027344000001</v>
       </c>
       <c r="N79">
-        <v>428.2408903999999</v>
+        <v>422.8472655999999</v>
       </c>
       <c r="O79">
-        <v>128.47226712</v>
+        <v>126.85417968</v>
       </c>
       <c r="P79">
-        <v>299.7686232799999</v>
+        <v>295.9930859199999</v>
       </c>
       <c r="Q79">
-        <v>771.46862328</v>
+        <v>767.6930859199999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1172515788845929</v>
+        <v>0.1202079629263954</v>
       </c>
       <c r="T79">
-        <v>1.650151937288519</v>
+        <v>1.718428704997584</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.031137724892321</v>
+        <v>2.005097497650112</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.06783255184380699</v>
+        <v>0.0756936405441576</v>
       </c>
       <c r="C80">
-        <v>502.8160668966902</v>
+        <v>-293.0719471053599</v>
       </c>
       <c r="D80">
-        <v>6020.284066896691</v>
+        <v>5295.552052894641</v>
       </c>
       <c r="E80">
-        <v>2001.368</v>
+        <v>2072.524</v>
       </c>
       <c r="F80">
-        <v>5550.168000000001</v>
+        <v>5621.324000000001</v>
       </c>
       <c r="G80">
         <v>32.7</v>
@@ -7853,45 +7853,45 @@
         <v>843.55</v>
       </c>
       <c r="M80">
-        <v>420.7027344000001</v>
+        <v>505.91916</v>
       </c>
       <c r="N80">
-        <v>422.8472655999999</v>
+        <v>337.6308399999999</v>
       </c>
       <c r="O80">
-        <v>126.85417968</v>
+        <v>101.289252</v>
       </c>
       <c r="P80">
-        <v>295.9930859199999</v>
+        <v>236.3415879999999</v>
       </c>
       <c r="Q80">
-        <v>767.6930859199999</v>
+        <v>708.0415879999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1202079629263954</v>
+        <v>0.1234459073531315</v>
       </c>
       <c r="T80">
-        <v>1.718428704997584</v>
+        <v>1.793208022012274</v>
       </c>
       <c r="U80">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V80">
         <v>0.3</v>
       </c>
       <c r="W80">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y80">
-        <v>2.005097497650112</v>
+        <v>1.667361244037486</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.0756936405441576</v>
+        <v>0.07580152924450823</v>
       </c>
       <c r="C81">
-        <v>-293.0719471053599</v>
+        <v>-372.9626479177841</v>
       </c>
       <c r="D81">
-        <v>5295.552052894641</v>
+        <v>5286.817352082217</v>
       </c>
       <c r="E81">
-        <v>2072.524</v>
+        <v>2143.68</v>
       </c>
       <c r="F81">
-        <v>5621.324000000001</v>
+        <v>5692.48</v>
       </c>
       <c r="G81">
         <v>32.7</v>
@@ -7935,28 +7935,28 @@
         <v>843.55</v>
       </c>
       <c r="M81">
-        <v>505.91916</v>
+        <v>512.3232</v>
       </c>
       <c r="N81">
-        <v>337.6308399999999</v>
+        <v>331.2267999999999</v>
       </c>
       <c r="O81">
-        <v>101.289252</v>
+        <v>99.36803999999997</v>
       </c>
       <c r="P81">
-        <v>236.3415879999999</v>
+        <v>231.85876</v>
       </c>
       <c r="Q81">
-        <v>708.0415879999999</v>
+        <v>703.5587599999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1234459073531315</v>
+        <v>0.1270076462225412</v>
       </c>
       <c r="T81">
-        <v>1.793208022012274</v>
+        <v>1.875465270728434</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.667361244037486</v>
+        <v>1.646519228487017</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07580152924450823</v>
+        <v>0.07590941794485886</v>
       </c>
       <c r="C82">
-        <v>-372.9626479177841</v>
+        <v>-452.8245814324264</v>
       </c>
       <c r="D82">
-        <v>5286.817352082217</v>
+        <v>5278.111418567574</v>
       </c>
       <c r="E82">
-        <v>2143.68</v>
+        <v>2214.836</v>
       </c>
       <c r="F82">
-        <v>5692.48</v>
+        <v>5763.636</v>
       </c>
       <c r="G82">
         <v>32.7</v>
@@ -8017,28 +8017,28 @@
         <v>843.55</v>
       </c>
       <c r="M82">
-        <v>512.3232</v>
+        <v>518.7272400000001</v>
       </c>
       <c r="N82">
-        <v>331.2267999999999</v>
+        <v>324.8227599999999</v>
       </c>
       <c r="O82">
-        <v>99.36803999999997</v>
+        <v>97.44682799999997</v>
       </c>
       <c r="P82">
-        <v>231.85876</v>
+        <v>227.3759319999999</v>
       </c>
       <c r="Q82">
-        <v>703.5587599999999</v>
+        <v>699.075932</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1270076462225412</v>
+        <v>0.1309443049729414</v>
       </c>
       <c r="T82">
-        <v>1.875465270728434</v>
+        <v>1.966381177204189</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.646519228487017</v>
+        <v>1.626191830604462</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07590941794485886</v>
+        <v>0.07601730664520949</v>
       </c>
       <c r="C83">
-        <v>-452.8245814324264</v>
+        <v>-532.6578895311204</v>
       </c>
       <c r="D83">
-        <v>5278.111418567574</v>
+        <v>5269.43411046888</v>
       </c>
       <c r="E83">
-        <v>2214.836</v>
+        <v>2285.992</v>
       </c>
       <c r="F83">
-        <v>5763.636</v>
+        <v>5834.792</v>
       </c>
       <c r="G83">
         <v>32.7</v>
@@ -8099,28 +8099,28 @@
         <v>843.55</v>
       </c>
       <c r="M83">
-        <v>518.7272400000001</v>
+        <v>525.1312800000001</v>
       </c>
       <c r="N83">
-        <v>324.8227599999999</v>
+        <v>318.4187199999999</v>
       </c>
       <c r="O83">
-        <v>97.44682799999997</v>
+        <v>95.52561599999997</v>
       </c>
       <c r="P83">
-        <v>227.3759319999999</v>
+        <v>222.8931039999999</v>
       </c>
       <c r="Q83">
-        <v>699.075932</v>
+        <v>694.5931039999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1309443049729414</v>
+        <v>0.1353183702511638</v>
       </c>
       <c r="T83">
-        <v>1.966381177204189</v>
+        <v>2.067398851066139</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.626191830604462</v>
+        <v>1.606360222914163</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07601730664520949</v>
+        <v>0.0761251953455601</v>
       </c>
       <c r="C84">
-        <v>-532.6578895311204</v>
+        <v>-612.4627131642001</v>
       </c>
       <c r="D84">
-        <v>5269.43411046888</v>
+        <v>5260.785286835801</v>
       </c>
       <c r="E84">
-        <v>2285.992</v>
+        <v>2357.148000000001</v>
       </c>
       <c r="F84">
-        <v>5834.792</v>
+        <v>5905.948000000001</v>
       </c>
       <c r="G84">
         <v>32.7</v>
@@ -8181,28 +8181,28 @@
         <v>843.55</v>
       </c>
       <c r="M84">
-        <v>525.1312800000001</v>
+        <v>531.5353200000001</v>
       </c>
       <c r="N84">
-        <v>318.4187199999999</v>
+        <v>312.0146799999999</v>
       </c>
       <c r="O84">
-        <v>95.52561599999997</v>
+        <v>93.60440399999996</v>
       </c>
       <c r="P84">
-        <v>222.8931039999999</v>
+        <v>218.4102759999999</v>
       </c>
       <c r="Q84">
-        <v>694.5931039999999</v>
+        <v>690.1102759999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1353183702511638</v>
+        <v>0.1402070314444712</v>
       </c>
       <c r="T84">
-        <v>2.067398851066139</v>
+        <v>2.180300957147142</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.606360222914163</v>
+        <v>1.587006485288691</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.0761251953455601</v>
+        <v>0.07623308404591074</v>
       </c>
       <c r="C85">
-        <v>-612.4627131642001</v>
+        <v>-692.2391923581481</v>
       </c>
       <c r="D85">
-        <v>5260.785286835801</v>
+        <v>5252.164807641853</v>
       </c>
       <c r="E85">
-        <v>2357.148000000001</v>
+        <v>2428.304000000001</v>
       </c>
       <c r="F85">
-        <v>5905.948000000001</v>
+        <v>5977.104000000001</v>
       </c>
       <c r="G85">
         <v>32.7</v>
@@ -8263,28 +8263,28 @@
         <v>843.55</v>
       </c>
       <c r="M85">
-        <v>531.5353200000001</v>
+        <v>537.9393600000001</v>
       </c>
       <c r="N85">
-        <v>312.0146799999999</v>
+        <v>305.6106399999999</v>
       </c>
       <c r="O85">
-        <v>93.60440399999996</v>
+        <v>91.68319199999996</v>
       </c>
       <c r="P85">
-        <v>218.4102759999999</v>
+        <v>213.9274479999999</v>
       </c>
       <c r="Q85">
-        <v>690.1102759999999</v>
+        <v>685.627448</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1402070314444712</v>
+        <v>0.1457067752869421</v>
       </c>
       <c r="T85">
-        <v>2.180300957147142</v>
+        <v>2.307315826488271</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.587006485288691</v>
+        <v>1.568113550940016</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07623308404591074</v>
+        <v>0.07634097274626137</v>
       </c>
       <c r="C86">
-        <v>-692.2391923581472</v>
+        <v>-771.9874662231305</v>
       </c>
       <c r="D86">
-        <v>5252.164807641853</v>
+        <v>5243.57253377687</v>
       </c>
       <c r="E86">
-        <v>2428.304</v>
+        <v>2499.46</v>
       </c>
       <c r="F86">
-        <v>5977.104</v>
+        <v>6048.26</v>
       </c>
       <c r="G86">
         <v>32.7</v>
@@ -8345,28 +8345,28 @@
         <v>843.55</v>
       </c>
       <c r="M86">
-        <v>537.93936</v>
+        <v>544.3434</v>
       </c>
       <c r="N86">
-        <v>305.61064</v>
+        <v>299.2066</v>
       </c>
       <c r="O86">
-        <v>91.68319199999999</v>
+        <v>89.76197999999999</v>
       </c>
       <c r="P86">
-        <v>213.927448</v>
+        <v>209.44462</v>
       </c>
       <c r="Q86">
-        <v>685.627448</v>
+        <v>681.14462</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1457067752869421</v>
+        <v>0.1519398183084091</v>
       </c>
       <c r="T86">
-        <v>2.307315826488269</v>
+        <v>2.451266011741549</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.568113550940017</v>
+        <v>1.549665156223075</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07634097274626137</v>
+        <v>0.07644886144661198</v>
       </c>
       <c r="C87">
-        <v>-771.9874662231305</v>
+        <v>-851.7076729605024</v>
       </c>
       <c r="D87">
-        <v>5243.57253377687</v>
+        <v>5235.008327039498</v>
       </c>
       <c r="E87">
-        <v>2499.46</v>
+        <v>2570.616</v>
       </c>
       <c r="F87">
-        <v>6048.26</v>
+        <v>6119.416</v>
       </c>
       <c r="G87">
         <v>32.7</v>
@@ -8427,28 +8427,28 @@
         <v>843.55</v>
       </c>
       <c r="M87">
-        <v>544.3434</v>
+        <v>550.74744</v>
       </c>
       <c r="N87">
-        <v>299.2066</v>
+        <v>292.80256</v>
       </c>
       <c r="O87">
-        <v>89.76197999999999</v>
+        <v>87.84076799999998</v>
       </c>
       <c r="P87">
-        <v>209.44462</v>
+        <v>204.961792</v>
       </c>
       <c r="Q87">
-        <v>681.14462</v>
+        <v>676.661792</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1519398183084091</v>
+        <v>0.1590632960472284</v>
       </c>
       <c r="T87">
-        <v>2.451266011741549</v>
+        <v>2.615780509173867</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.549665156223075</v>
+        <v>1.531645793941412</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07644886144661198</v>
+        <v>0.07655675014696262</v>
       </c>
       <c r="C88">
-        <v>-851.7076729605024</v>
+        <v>-931.3999498702015</v>
       </c>
       <c r="D88">
-        <v>5235.008327039498</v>
+        <v>5226.472050129799</v>
       </c>
       <c r="E88">
-        <v>2570.616</v>
+        <v>2641.772</v>
       </c>
       <c r="F88">
-        <v>6119.416</v>
+        <v>6190.572</v>
       </c>
       <c r="G88">
         <v>32.7</v>
@@ -8509,28 +8509,28 @@
         <v>843.55</v>
       </c>
       <c r="M88">
-        <v>550.74744</v>
+        <v>557.15148</v>
       </c>
       <c r="N88">
-        <v>292.80256</v>
+        <v>286.39852</v>
       </c>
       <c r="O88">
-        <v>87.84076799999998</v>
+        <v>85.91955599999999</v>
       </c>
       <c r="P88">
-        <v>204.961792</v>
+        <v>200.478964</v>
       </c>
       <c r="Q88">
-        <v>676.661792</v>
+        <v>672.178964</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1590632960472284</v>
+        <v>0.1672826934381739</v>
       </c>
       <c r="T88">
-        <v>2.615780509173867</v>
+        <v>2.805604929288081</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.531645793941412</v>
+        <v>1.51404066987312</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07655675014696262</v>
+        <v>0.1153082642641147</v>
       </c>
       <c r="C89">
-        <v>-931.3999498702015</v>
+        <v>-2932.993008663187</v>
       </c>
       <c r="D89">
-        <v>5226.472050129799</v>
+        <v>3296.034991336813</v>
       </c>
       <c r="E89">
-        <v>2641.772</v>
+        <v>2712.928</v>
       </c>
       <c r="F89">
-        <v>6190.572</v>
+        <v>6261.728</v>
       </c>
       <c r="G89">
         <v>32.7</v>
@@ -8591,45 +8591,45 @@
         <v>843.55</v>
       </c>
       <c r="M89">
-        <v>557.15148</v>
+        <v>919.2216704000001</v>
       </c>
       <c r="N89">
-        <v>286.39852</v>
+        <v>-75.67167040000015</v>
       </c>
       <c r="O89">
-        <v>85.91955599999999</v>
+        <v>-22.70150112000005</v>
       </c>
       <c r="P89">
-        <v>200.478964</v>
+        <v>-52.97016928000011</v>
       </c>
       <c r="Q89">
-        <v>672.178964</v>
+        <v>418.7298307199999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.1672826934381739</v>
+        <v>0.1807423299952855</v>
       </c>
       <c r="T89">
-        <v>2.805604929288081</v>
+        <v>3.116451039152089</v>
       </c>
       <c r="U89">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.3</v>
+        <v>0.2753035618599793</v>
       </c>
       <c r="W89">
-        <v>0.063</v>
+        <v>0.1063854371189551</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y89">
-        <v>1.51404066987312</v>
+        <v>0.9176785395332645</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1153082642641147</v>
+        <v>0.1163182642641147</v>
       </c>
       <c r="C90">
-        <v>-2932.993008663187</v>
+        <v>-3035.576569543495</v>
       </c>
       <c r="D90">
-        <v>3296.034991336813</v>
+        <v>3264.607430456505</v>
       </c>
       <c r="E90">
-        <v>2712.928</v>
+        <v>2784.084</v>
       </c>
       <c r="F90">
-        <v>6261.728</v>
+        <v>6332.884</v>
       </c>
       <c r="G90">
         <v>32.7</v>
@@ -8673,37 +8673,37 @@
         <v>843.55</v>
       </c>
       <c r="M90">
-        <v>919.2216704000001</v>
+        <v>929.6673712</v>
       </c>
       <c r="N90">
-        <v>-75.67167040000015</v>
+        <v>-86.11737120000009</v>
       </c>
       <c r="O90">
-        <v>-22.70150112000005</v>
+        <v>-25.83521136000003</v>
       </c>
       <c r="P90">
-        <v>-52.97016928000011</v>
+        <v>-60.28215984000006</v>
       </c>
       <c r="Q90">
-        <v>418.7298307199999</v>
+        <v>411.4178401599999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.1807423299952855</v>
+        <v>0.1930098145403114</v>
       </c>
       <c r="T90">
-        <v>3.116451039152089</v>
+        <v>3.399764769984097</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.2753035618599793</v>
+        <v>0.2722102634121145</v>
       </c>
       <c r="W90">
-        <v>0.1063854371189551</v>
+        <v>0.1068395333311016</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.9176785395332645</v>
+        <v>0.9073675447070482</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1163182642641147</v>
+        <v>0.1173282642641147</v>
       </c>
       <c r="C91">
-        <v>-3035.576569543495</v>
+        <v>-3137.566469898773</v>
       </c>
       <c r="D91">
-        <v>3264.607430456505</v>
+        <v>3233.773530101229</v>
       </c>
       <c r="E91">
-        <v>2784.084</v>
+        <v>2855.240000000001</v>
       </c>
       <c r="F91">
-        <v>6332.884</v>
+        <v>6404.040000000001</v>
       </c>
       <c r="G91">
         <v>32.7</v>
@@ -8755,37 +8755,37 @@
         <v>843.55</v>
       </c>
       <c r="M91">
-        <v>929.6673712</v>
+        <v>940.1130720000002</v>
       </c>
       <c r="N91">
-        <v>-86.11737120000009</v>
+        <v>-96.56307200000026</v>
       </c>
       <c r="O91">
-        <v>-25.83521136000003</v>
+        <v>-28.96892160000008</v>
       </c>
       <c r="P91">
-        <v>-60.28215984000006</v>
+        <v>-67.59415040000019</v>
       </c>
       <c r="Q91">
-        <v>411.4178401599999</v>
+        <v>404.1058495999998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.1930098145403114</v>
+        <v>0.2077307959943426</v>
       </c>
       <c r="T91">
-        <v>3.399764769984097</v>
+        <v>3.739741246982507</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2722102634121145</v>
+        <v>0.2691857049297576</v>
       </c>
       <c r="W91">
-        <v>0.1068395333311016</v>
+        <v>0.1072835385163116</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.9073675447070482</v>
+        <v>0.8972856830991919</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1173282642641147</v>
+        <v>0.1183382642641147</v>
       </c>
       <c r="C92">
-        <v>-3137.566469898773</v>
+        <v>-3238.979373539084</v>
       </c>
       <c r="D92">
-        <v>3233.773530101229</v>
+        <v>3203.516626460917</v>
       </c>
       <c r="E92">
-        <v>2855.240000000001</v>
+        <v>2926.396000000001</v>
       </c>
       <c r="F92">
-        <v>6404.040000000001</v>
+        <v>6475.196000000001</v>
       </c>
       <c r="G92">
         <v>32.7</v>
@@ -8837,37 +8837,37 @@
         <v>843.55</v>
       </c>
       <c r="M92">
-        <v>940.1130720000002</v>
+        <v>950.5587728000002</v>
       </c>
       <c r="N92">
-        <v>-96.56307200000026</v>
+        <v>-107.0087728000002</v>
       </c>
       <c r="O92">
-        <v>-28.96892160000008</v>
+        <v>-32.10263184000006</v>
       </c>
       <c r="P92">
-        <v>-67.59415040000019</v>
+        <v>-74.90614096000014</v>
       </c>
       <c r="Q92">
-        <v>404.1058495999998</v>
+        <v>396.7938590399999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2077307959943426</v>
+        <v>0.2257231066603806</v>
       </c>
       <c r="T92">
-        <v>3.739741246982507</v>
+        <v>4.155268052202786</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2691857049297576</v>
+        <v>0.2662276202601998</v>
       </c>
       <c r="W92">
-        <v>0.1072835385163116</v>
+        <v>0.1077177853458027</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8972856830991919</v>
+        <v>0.8874254008673327</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1183382642641147</v>
+        <v>0.1193482642641147</v>
       </c>
       <c r="C93">
-        <v>-3238.979373539084</v>
+        <v>-3339.831326393867</v>
       </c>
       <c r="D93">
-        <v>3203.516626460917</v>
+        <v>3173.820673606134</v>
       </c>
       <c r="E93">
-        <v>2926.396000000001</v>
+        <v>2997.552000000001</v>
       </c>
       <c r="F93">
-        <v>6475.196000000001</v>
+        <v>6546.352000000001</v>
       </c>
       <c r="G93">
         <v>32.7</v>
@@ -8919,37 +8919,37 @@
         <v>843.55</v>
       </c>
       <c r="M93">
-        <v>950.5587728000002</v>
+        <v>961.0044736000002</v>
       </c>
       <c r="N93">
-        <v>-107.0087728000002</v>
+        <v>-117.4544736000003</v>
       </c>
       <c r="O93">
-        <v>-32.10263184000006</v>
+        <v>-35.23634208000008</v>
       </c>
       <c r="P93">
-        <v>-74.90614096000014</v>
+        <v>-82.21813152000018</v>
       </c>
       <c r="Q93">
-        <v>396.7938590399999</v>
+        <v>389.4818684799998</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2257231066603806</v>
+        <v>0.2482134949929283</v>
       </c>
       <c r="T93">
-        <v>4.155268052202786</v>
+        <v>4.674676558728136</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2662276202601998</v>
+        <v>0.2633338417791107</v>
       </c>
       <c r="W93">
-        <v>0.1077177853458027</v>
+        <v>0.1081425920268266</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8874254008673327</v>
+        <v>0.8777794725970356</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1193482642641147</v>
+        <v>0.1203582642641147</v>
       </c>
       <c r="C94">
-        <v>-3339.831326393867</v>
+        <v>-3440.137784887038</v>
       </c>
       <c r="D94">
-        <v>3173.820673606134</v>
+        <v>3144.670215112963</v>
       </c>
       <c r="E94">
-        <v>2997.552000000001</v>
+        <v>3068.708000000001</v>
       </c>
       <c r="F94">
-        <v>6546.352000000001</v>
+        <v>6617.508000000001</v>
       </c>
       <c r="G94">
         <v>32.7</v>
@@ -9001,37 +9001,37 @@
         <v>843.55</v>
       </c>
       <c r="M94">
-        <v>961.0044736000002</v>
+        <v>971.4501744000002</v>
       </c>
       <c r="N94">
-        <v>-117.4544736000003</v>
+        <v>-127.9001744000002</v>
       </c>
       <c r="O94">
-        <v>-35.23634208000008</v>
+        <v>-38.37005232000006</v>
       </c>
       <c r="P94">
-        <v>-82.21813152000018</v>
+        <v>-89.53012208000014</v>
       </c>
       <c r="Q94">
-        <v>389.4818684799998</v>
+        <v>382.1698779199999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.2482134949929283</v>
+        <v>0.2771297085633467</v>
       </c>
       <c r="T94">
-        <v>4.674676558728136</v>
+        <v>5.3424874956893</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2633338417791107</v>
+        <v>0.2605022950933138</v>
       </c>
       <c r="W94">
-        <v>0.1081425920268266</v>
+        <v>0.1085582630803015</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8777794725970356</v>
+        <v>0.8683409836443793</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1203582642641147</v>
+        <v>0.1213682642641147</v>
       </c>
       <c r="C95">
-        <v>-3440.137784887038</v>
+        <v>-3539.913642762647</v>
       </c>
       <c r="D95">
-        <v>3144.670215112963</v>
+        <v>3116.050357237354</v>
       </c>
       <c r="E95">
-        <v>3068.708000000001</v>
+        <v>3139.864</v>
       </c>
       <c r="F95">
-        <v>6617.508000000001</v>
+        <v>6688.664000000001</v>
       </c>
       <c r="G95">
         <v>32.7</v>
@@ -9083,37 +9083,37 @@
         <v>843.55</v>
       </c>
       <c r="M95">
-        <v>971.4501744000002</v>
+        <v>981.8958752000002</v>
       </c>
       <c r="N95">
-        <v>-127.9001744000002</v>
+        <v>-138.3458752000003</v>
       </c>
       <c r="O95">
-        <v>-38.37005232000006</v>
+        <v>-41.50376256000008</v>
       </c>
       <c r="P95">
-        <v>-89.53012208000014</v>
+        <v>-96.84211264000018</v>
       </c>
       <c r="Q95">
-        <v>382.1698779199999</v>
+        <v>374.8578873599998</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.2771297085633467</v>
+        <v>0.3156846599905712</v>
       </c>
       <c r="T95">
-        <v>5.3424874956893</v>
+        <v>6.232902078304184</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2605022950933138</v>
+        <v>0.2577309940816828</v>
       </c>
       <c r="W95">
-        <v>0.1085582630803015</v>
+        <v>0.108965090068809</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8683409836443793</v>
+        <v>0.8591033136056092</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1213682642641147</v>
+        <v>0.1223782642641147</v>
       </c>
       <c r="C96">
-        <v>-3539.913642762647</v>
+        <v>-3639.173256458885</v>
       </c>
       <c r="D96">
-        <v>3116.050357237354</v>
+        <v>3087.946743541116</v>
       </c>
       <c r="E96">
-        <v>3139.864</v>
+        <v>3211.02</v>
       </c>
       <c r="F96">
-        <v>6688.664000000001</v>
+        <v>6759.820000000001</v>
       </c>
       <c r="G96">
         <v>32.7</v>
@@ -9165,37 +9165,37 @@
         <v>843.55</v>
       </c>
       <c r="M96">
-        <v>981.8958752000002</v>
+        <v>992.3415760000001</v>
       </c>
       <c r="N96">
-        <v>-138.3458752000003</v>
+        <v>-148.7915760000002</v>
       </c>
       <c r="O96">
-        <v>-41.50376256000008</v>
+        <v>-44.63747280000005</v>
       </c>
       <c r="P96">
-        <v>-96.84211264000018</v>
+        <v>-104.1541032000001</v>
       </c>
       <c r="Q96">
-        <v>374.8578873599998</v>
+        <v>367.5458967999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3156846599905712</v>
+        <v>0.3696615919886855</v>
       </c>
       <c r="T96">
-        <v>6.232902078304184</v>
+        <v>7.479482493965024</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2577309940816828</v>
+        <v>0.255018036249244</v>
       </c>
       <c r="W96">
-        <v>0.108965090068809</v>
+        <v>0.109363352278611</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8591033136056092</v>
+        <v>0.8500601208308134</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1223782642641147</v>
+        <v>0.1233882642641147</v>
       </c>
       <c r="C97">
-        <v>-3639.173256458885</v>
+        <v>-3737.930469121275</v>
       </c>
       <c r="D97">
-        <v>3087.946743541116</v>
+        <v>3060.345530878726</v>
       </c>
       <c r="E97">
-        <v>3211.02</v>
+        <v>3282.176</v>
       </c>
       <c r="F97">
-        <v>6759.820000000001</v>
+        <v>6830.976000000001</v>
       </c>
       <c r="G97">
         <v>32.7</v>
@@ -9247,37 +9247,37 @@
         <v>843.55</v>
       </c>
       <c r="M97">
-        <v>992.3415760000001</v>
+        <v>1002.7872768</v>
       </c>
       <c r="N97">
-        <v>-148.7915760000002</v>
+        <v>-159.2372768000002</v>
       </c>
       <c r="O97">
-        <v>-44.63747280000005</v>
+        <v>-47.77118304000007</v>
       </c>
       <c r="P97">
-        <v>-104.1541032000001</v>
+        <v>-111.4660937600002</v>
       </c>
       <c r="Q97">
-        <v>367.5458967999999</v>
+        <v>360.2339062399998</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.3696615919886855</v>
+        <v>0.4506269899858571</v>
       </c>
       <c r="T97">
-        <v>7.479482493965024</v>
+        <v>9.349353117456284</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.255018036249244</v>
+        <v>0.2523615983716477</v>
       </c>
       <c r="W97">
-        <v>0.109363352278611</v>
+        <v>0.1097533173590421</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8500601208308134</v>
+        <v>0.8412053279054924</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1233882642641147</v>
+        <v>0.1243982642641147</v>
       </c>
       <c r="C98">
-        <v>-3737.930469121273</v>
+        <v>-3836.198633339445</v>
       </c>
       <c r="D98">
-        <v>3060.345530878727</v>
+        <v>3033.233366660556</v>
       </c>
       <c r="E98">
-        <v>3282.175999999999</v>
+        <v>3353.332</v>
       </c>
       <c r="F98">
-        <v>6830.976</v>
+        <v>6902.132000000001</v>
       </c>
       <c r="G98">
         <v>32.7</v>
@@ -9329,37 +9329,37 @@
         <v>843.55</v>
       </c>
       <c r="M98">
-        <v>1002.7872768</v>
+        <v>1013.2329776</v>
       </c>
       <c r="N98">
-        <v>-159.2372768000001</v>
+        <v>-169.6829776000002</v>
       </c>
       <c r="O98">
-        <v>-47.77118304000004</v>
+        <v>-50.90489328000005</v>
       </c>
       <c r="P98">
-        <v>-111.4660937600001</v>
+        <v>-118.7780843200001</v>
       </c>
       <c r="Q98">
-        <v>360.2339062399999</v>
+        <v>352.9219156799999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.450626989985856</v>
+        <v>0.5855693199811414</v>
       </c>
       <c r="T98">
-        <v>9.349353117456259</v>
+        <v>12.46580415660835</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2523615983716477</v>
+        <v>0.2497599324090534</v>
       </c>
       <c r="W98">
-        <v>0.1097533173590421</v>
+        <v>0.110135241922351</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8412053279054925</v>
+        <v>0.8325331080301781</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1243982642641147</v>
+        <v>0.1254082642641147</v>
       </c>
       <c r="C99">
-        <v>-3836.198633339445</v>
+        <v>-3933.990632685941</v>
       </c>
       <c r="D99">
-        <v>3033.233366660556</v>
+        <v>3006.597367314059</v>
       </c>
       <c r="E99">
-        <v>3353.332</v>
+        <v>3424.488</v>
       </c>
       <c r="F99">
-        <v>6902.132000000001</v>
+        <v>6973.288</v>
       </c>
       <c r="G99">
         <v>32.7</v>
@@ -9411,37 +9411,37 @@
         <v>843.55</v>
       </c>
       <c r="M99">
-        <v>1013.2329776</v>
+        <v>1023.6786784</v>
       </c>
       <c r="N99">
-        <v>-169.6829776000002</v>
+        <v>-180.1286784000002</v>
       </c>
       <c r="O99">
-        <v>-50.90489328000005</v>
+        <v>-54.03860352000007</v>
       </c>
       <c r="P99">
-        <v>-118.7780843200001</v>
+        <v>-126.0900748800002</v>
       </c>
       <c r="Q99">
-        <v>352.9219156799999</v>
+        <v>345.6099251199998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.5855693199811414</v>
+        <v>0.8554539799717119</v>
       </c>
       <c r="T99">
-        <v>12.46580415660835</v>
+        <v>18.69870623491252</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2497599324090534</v>
+        <v>0.2472113616701855</v>
       </c>
       <c r="W99">
-        <v>0.110135241922351</v>
+        <v>0.1105093721068168</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8325331080301781</v>
+        <v>0.8240378722339518</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1254082642641147</v>
+        <v>0.1264182642641147</v>
       </c>
       <c r="C100">
-        <v>-3933.990632685941</v>
+        <v>-4031.318902130065</v>
       </c>
       <c r="D100">
-        <v>3006.597367314059</v>
+        <v>2980.425097869935</v>
       </c>
       <c r="E100">
-        <v>3424.488</v>
+        <v>3495.644</v>
       </c>
       <c r="F100">
-        <v>6973.288</v>
+        <v>7044.444</v>
       </c>
       <c r="G100">
         <v>32.7</v>
@@ -9493,37 +9493,37 @@
         <v>843.55</v>
       </c>
       <c r="M100">
-        <v>1023.6786784</v>
+        <v>1034.1243792</v>
       </c>
       <c r="N100">
-        <v>-180.1286784000002</v>
+        <v>-190.5743792000003</v>
       </c>
       <c r="O100">
-        <v>-54.03860352000007</v>
+        <v>-57.17231376000009</v>
       </c>
       <c r="P100">
-        <v>-126.0900748800002</v>
+        <v>-133.4020654400002</v>
       </c>
       <c r="Q100">
-        <v>345.6099251199998</v>
+        <v>338.2979345599998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>0.8554539799717119</v>
+        <v>1.665107959943424</v>
       </c>
       <c r="T100">
-        <v>18.69870623491252</v>
+        <v>37.39741246982503</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.2472113616701855</v>
+        <v>0.2447142772088705</v>
       </c>
       <c r="W100">
-        <v>0.1105093721068168</v>
+        <v>0.1108759441057378</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8240378722339518</v>
+        <v>0.8157142573629017</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1264182642641147</v>
-      </c>
-      <c r="C101">
-        <v>-4031.318902130065</v>
-      </c>
-      <c r="D101">
-        <v>2980.425097869935</v>
-      </c>
-      <c r="E101">
-        <v>3495.644</v>
-      </c>
-      <c r="F101">
-        <v>7044.444</v>
-      </c>
-      <c r="G101">
-        <v>32.7</v>
-      </c>
-      <c r="H101">
-        <v>3566.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1315.25</v>
-      </c>
-      <c r="K101">
-        <v>471.7</v>
-      </c>
-      <c r="L101">
-        <v>843.55</v>
-      </c>
-      <c r="M101">
-        <v>1034.1243792</v>
-      </c>
-      <c r="N101">
-        <v>-190.5743792000003</v>
-      </c>
-      <c r="O101">
-        <v>-57.17231376000009</v>
-      </c>
-      <c r="P101">
-        <v>-133.4020654400002</v>
-      </c>
-      <c r="Q101">
-        <v>338.2979345599998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>1.665107959943424</v>
-      </c>
-      <c r="T101">
-        <v>37.39741246982503</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2447142772088705</v>
-      </c>
-      <c r="W101">
-        <v>0.1108759441057378</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8157142573629017</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
